--- a/Dữ liệu mẫu/Mapping.xlsx
+++ b/Dữ liệu mẫu/Mapping.xlsx
@@ -2012,7 +2012,7 @@
 3. Ghi kết quả vào: data.summary.sections[order=3].latestBySpecialty[].trends[].name</t>
   </si>
   <si>
-    <t>trends[].name = tên chỉ số được so sánh | Lưu ý: chỉ Huyết áp, Cân nặng và chỉ số lab có dữ liệu ở cả hai lượt; không tự tạo tên.</t>
+    <t>trends[].name = tên chỉ số được so sánh | Lưu ý: chỉ Huyết áp, Cân nặng,  và chỉ số lab(Cận lâm sàn) có dữ liệu ở cả hai lượt; không tự tạo tên.</t>
   </si>
   <si>
     <t>data.summary.sections[order=3].latestBySpecialty[].trends[].from</t>
@@ -7163,12 +7163,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:N100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.85185185185185" style="16" customWidth="1"/>
-    <col min="2" max="2" width="45.8518518518519" style="16" customWidth="1"/>
+    <col min="2" max="2" width="73.3240740740741" style="16" customWidth="1"/>
     <col min="3" max="3" width="18.712962962963" style="16" customWidth="1"/>
     <col min="4" max="4" width="50" style="16" customWidth="1"/>
     <col min="5" max="5" width="14.712962962963" style="16" customWidth="1"/>
@@ -7178,7 +7178,9 @@
     <col min="10" max="10" width="53.5740740740741" style="16" customWidth="1"/>
     <col min="11" max="11" width="41.5740740740741" style="16" customWidth="1"/>
     <col min="12" max="12" width="62" style="16" customWidth="1"/>
-    <col min="13" max="16384" width="9.13888888888889" style="16" customWidth="1"/>
+    <col min="13" max="13" width="9.13888888888889" style="16" customWidth="1"/>
+    <col min="14" max="14" width="33.4907407407407" style="16" customWidth="1"/>
+    <col min="15" max="16384" width="9.13888888888889" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -7374,7 +7376,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" s="14" customFormat="1" ht="409.5" hidden="1" customHeight="1" spans="1:13">
+    <row r="6" s="14" customFormat="1" ht="409.5" customHeight="1" spans="1:13">
       <c r="A6" s="23">
         <v>5</v>
       </c>
@@ -7410,7 +7412,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="7" s="14" customFormat="1" ht="336" hidden="1" customHeight="1" spans="1:13">
+    <row r="7" s="14" customFormat="1" ht="336" customHeight="1" spans="1:13">
       <c r="A7" s="23">
         <v>6</v>
       </c>
@@ -7484,7 +7486,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="9" s="14" customFormat="1" ht="152.25" hidden="1" customHeight="1" spans="1:13">
+    <row r="9" s="14" customFormat="1" ht="152.25" customHeight="1" spans="1:13">
       <c r="A9" s="23">
         <v>8</v>
       </c>
@@ -7521,7 +7523,7 @@
       </c>
       <c r="M9" s="34"/>
     </row>
-    <row r="10" s="14" customFormat="1" ht="244.5" hidden="1" customHeight="1" spans="1:13">
+    <row r="10" s="14" customFormat="1" ht="244.5" customHeight="1" spans="1:13">
       <c r="A10" s="23">
         <v>9</v>
       </c>
@@ -7558,7 +7560,7 @@
       </c>
       <c r="M10" s="34"/>
     </row>
-    <row r="11" s="14" customFormat="1" ht="60.75" hidden="1" customHeight="1" spans="1:13">
+    <row r="11" s="14" customFormat="1" ht="60.75" customHeight="1" spans="1:13">
       <c r="A11" s="23">
         <v>10</v>
       </c>
@@ -7595,7 +7597,7 @@
       </c>
       <c r="M11" s="34"/>
     </row>
-    <row r="12" ht="106.5" hidden="1" customHeight="1" spans="1:13">
+    <row r="12" ht="106.5" customHeight="1" spans="1:13">
       <c r="A12" s="23">
         <v>11</v>
       </c>
@@ -7632,7 +7634,7 @@
       </c>
       <c r="M12" s="35"/>
     </row>
-    <row r="13" ht="137.25" hidden="1" customHeight="1" spans="1:13">
+    <row r="13" ht="137.25" customHeight="1" spans="1:13">
       <c r="A13" s="23">
         <v>12</v>
       </c>
@@ -7742,7 +7744,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="16" ht="409.5" hidden="1" customHeight="1" spans="1:13">
+    <row r="16" ht="409.5" customHeight="1" spans="1:13">
       <c r="A16" s="23">
         <v>15</v>
       </c>
@@ -7778,7 +7780,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="17" ht="121.5" hidden="1" customHeight="1" spans="1:13">
+    <row r="17" ht="121.5" customHeight="1" spans="1:13">
       <c r="A17" s="23">
         <v>16</v>
       </c>
@@ -7817,7 +7819,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="18" ht="198" hidden="1" customHeight="1" spans="1:13">
+    <row r="18" ht="198" customHeight="1" spans="1:13">
       <c r="A18" s="23">
         <v>17</v>
       </c>
@@ -7853,7 +7855,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="19" ht="183" hidden="1" customHeight="1" spans="1:13">
+    <row r="19" ht="183" customHeight="1" spans="1:13">
       <c r="A19" s="23">
         <v>18</v>
       </c>
@@ -7889,7 +7891,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20" ht="183" hidden="1" customHeight="1" spans="1:13">
+    <row r="20" ht="183" customHeight="1" spans="1:13">
       <c r="A20" s="23">
         <v>19</v>
       </c>
@@ -8802,7 +8804,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="44" ht="305.25" hidden="1" customHeight="1" spans="1:13">
+    <row r="44" ht="305.25" customHeight="1" spans="1:13">
       <c r="A44" s="23">
         <v>43</v>
       </c>
@@ -8838,7 +8840,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="45" ht="305.25" hidden="1" customHeight="1" spans="1:13">
+    <row r="45" ht="305.25" customHeight="1" spans="1:13">
       <c r="A45" s="23">
         <v>44</v>
       </c>
@@ -9026,7 +9028,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="50" ht="229.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="50" ht="229.5" customHeight="1" spans="1:14">
       <c r="A50" s="23">
         <v>49</v>
       </c>
@@ -9062,7 +9064,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="51" ht="229.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="51" ht="229.5" customHeight="1" spans="1:14">
       <c r="A51" s="23">
         <v>50</v>
       </c>
@@ -9098,7 +9100,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="52" ht="290.25" hidden="1" customHeight="1" spans="1:14">
+    <row r="52" ht="290.25" customHeight="1" spans="1:14">
       <c r="A52" s="23">
         <v>51</v>
       </c>
@@ -9576,7 +9578,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="64" ht="229.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="64" ht="229.5" customHeight="1" spans="1:14">
       <c r="A64" s="23">
         <v>63</v>
       </c>
@@ -9802,7 +9804,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="70" ht="121.5" hidden="1" customHeight="1" spans="1:12">
+    <row r="70" ht="121.5" customHeight="1" spans="1:12">
       <c r="A70" s="23">
         <v>69</v>
       </c>
@@ -9952,7 +9954,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="74" ht="409.5" hidden="1" customHeight="1" spans="1:12">
+    <row r="74" ht="409.5" customHeight="1" spans="1:12">
       <c r="A74" s="23">
         <v>73</v>
       </c>
@@ -9988,7 +9990,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="75" ht="305.25" hidden="1" customHeight="1" spans="1:12">
+    <row r="75" ht="305.25" customHeight="1" spans="1:12">
       <c r="A75" s="23">
         <v>74</v>
       </c>
@@ -10024,7 +10026,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="76" ht="351" hidden="1" customHeight="1" spans="1:12">
+    <row r="76" ht="351" customHeight="1" spans="1:12">
       <c r="A76" s="23">
         <v>75</v>
       </c>
@@ -10060,7 +10062,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="77" ht="351" hidden="1" customHeight="1" spans="1:12">
+    <row r="77" ht="351" customHeight="1" spans="1:12">
       <c r="A77" s="23">
         <v>76</v>
       </c>
@@ -10292,7 +10294,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="83" ht="381.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="83" ht="381.75" customHeight="1" spans="1:14">
       <c r="A83" s="23">
         <v>82</v>
       </c>
@@ -10480,7 +10482,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="88" ht="275.25" hidden="1" customHeight="1" spans="1:14">
+    <row r="88" ht="275.25" customHeight="1" spans="1:14">
       <c r="A88" s="23">
         <v>87</v>
       </c>
@@ -10516,7 +10518,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="89" ht="409.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="89" ht="409.5" customHeight="1" spans="1:14">
       <c r="A89" s="23">
         <v>88</v>
       </c>
@@ -10942,12 +10944,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N99" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="n/a"/>
-        <filter val="N"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Dữ liệu mẫu/Mapping.xlsx
+++ b/Dữ liệu mẫu/Mapping.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="1314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2316" uniqueCount="1303">
   <si>
     <t>Cột</t>
   </si>
@@ -549,7 +549,7 @@
                         }</t>
   </si>
   <si>
-    <t>No.</t>
+    <t xml:space="preserve">No. </t>
   </si>
   <si>
     <t>Output field</t>
@@ -670,7 +670,7 @@
 3. Ghi kết quả vào: data.summary.latestVisitDate</t>
   </si>
   <si>
-    <t>data.summary.latestVisitDate = max(visits[].visit_date) | Lưu ý: chỉ dùng ngày hợp lệ lấy ngày tái khám mới nhất ; không có thì trả "".</t>
+    <t>data.summary.latestVisitDate = max(visits[].visit_date) | Lưu ý: chỉ dùng ngày hợp lệ lấy ngày khám mới nhất ; không có thì trả "".</t>
   </si>
   <si>
     <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
@@ -1354,7 +1354,7 @@
 3. Ghi kết quả vào: data.summary.sections[order=3].latestBySpecialty[]</t>
   </si>
   <si>
-    <t>data.summary.sections[order=3].latestBySpecialty[] = chọn/lọc(visits[] + visits[].prescriptions[].prescribed_date + visits[].prescriptions[].items[].stop_date) | Lưu ý: Bước 1: Chọn lượt khám có visit_date mới nhất. Bước 3: Bỏ lượt bị trùng và sắp xếp các lượt theo ngày giảm dần.</t>
+    <t>latestBySpecialty[] = lượt có visit_date mới nhất toàn bộ + các lượt có ít nhất một thuốc còn hiệu lực theo stop_date | Lưu ý: khử trùng theo lượt, sắp xếp visit_date giảm dần; không xác định được stop_date thì không chọn thêm lượt cũ.</t>
   </si>
   <si>
     <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
@@ -1855,14 +1855,17 @@
     <t>Dùng tên chẩn đoán nguồn làm mô tả; giữ phần diagnosis_text có ý nghĩa chưa được phản ánh, chỉ gắn vào đúng chẩn đoán khi truy vết được.</t>
   </si>
   <si>
-    <t>1. Đọc dữ liệu từ: visits[].diagnosis.diagnosis_primary[].description và visits[].diagnosis.diagnosis_comorbidities[].description
+    <t>1. Đọc dữ liệu từ:
+visits[].diagnosis.diagnosis_primary[].description;
+visits[].diagnosis.diagnosis_comorbidities[].description
 2. Xử lý:
-Không tạo field name riêng trong output diagnosis.
-Dùng name của nguồn để tạo hoặc bổ sung description theo đúng chẩn đoán và đúng lượt khám.
-3. Ghi kết quả vào: diagnoses[].description; không tạo diagnoses[].name</t>
-  </si>
-  <si>
-    <t>data.summary.sections[order=3].latestBySpecialty[].diagnoses[].description = diagnosis_primary[].description + diagnosis_comorbidities[].description | Lưu ý: giữ đúng chẩn đoán, đúng lượt khám và khử trùng.</t>
+Với từng chẩn đoán của đúng lượt khám, lấy description nếu có ý nghĩa.
+Bỏ giá trị rỗng và khử trùng, nhưng vẫn giữ đúng quan hệ với chẩn đoán nguồn.
+3. Ghi kết quả vào:
+data.summary.sections[order=3].latestBySpecialty[].diagnoses[].description</t>
+  </si>
+  <si>
+    <t>diagnoses[].description = unique(diagnosis_primary[].description + diagnosis_comorbidities[].description) | Lưu ý: bỏ giá trị rỗng, giữ đúng chẩn đoán và đúng lượt khám.</t>
   </si>
   <si>
     <t>data.summary.sections[order=3].latestBySpecialty[].diagnoses[].description
@@ -1882,16 +1885,17 @@
     <t>KHÔNG sinh name riêng theo output contract; bảo toàn tên bệnh trong description.</t>
   </si>
   <si>
-    <t>1. Đọc dữ liệu từ: visits[].diagnosis.diagnosis_primary[].name và visits[].diagnosis.diagnosis_comorbidities[].name
+    <t>1. Đọc dữ liệu từ:
+visits[].diagnosis.diagnosis_primary[].name;
+visits[].diagnosis.diagnosis_comorbidities[].name
 2. Xử lý:
-lấy từ 
-visits[].diagnosis.diagnosis_primary[].name → diagnoses[].name
-visits[].diagnosis.diagnosis_comorbidities[].name → diagnoses[].name
-loại bỏ những kết quả trùng lắp
-3. Ghi kết quả vào: diagnoses[].description; không tạo diagnoses[].name</t>
-  </si>
-  <si>
-    <t>diagnoses[].description = unique(diagnosis_primary[].name + diagnosis_comorbidities[].name) | Lưu ý: bỏ giá trị rỗng, giữ đúng lượt khám và không tạo diagnoses[].name.</t>
+Với từng chẩn đoán của đúng lượt khám, lấy nguyên name từ nguồn.
+Bỏ giá trị rỗng và loại bỏ kết quả trùng lặp.
+3. Ghi kết quả vào:
+data.summary.sections[order=3].latestBySpecialty[].diagnoses[].name</t>
+  </si>
+  <si>
+    <t>diagnoses[].name = unique(diagnosis_primary[].name + diagnosis_comorbidities[].name) | Lưu ý: bỏ giá trị rỗng, giữ đúng chẩn đoán và đúng lượt khám.</t>
   </si>
   <si>
     <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
@@ -2012,7 +2016,7 @@
 3. Ghi kết quả vào: data.summary.sections[order=3].latestBySpecialty[].trends[].name</t>
   </si>
   <si>
-    <t>trends[].name = tên chỉ số được so sánh | Lưu ý: chỉ Huyết áp, Cân nặng,  và chỉ số lab(Cận lâm sàn) có dữ liệu ở cả hai lượt; không tự tạo tên.</t>
+    <t>trends[].name = tên chỉ số có giá trị ở cả lượt đang xét và lượt gần nhất trước đó cùng specialty | Lưu ý: chỉ so sánh Huyết áp, Cân nặng và các chỉ số lab; specialty và visit_date chỉ dùng để chọn đúng cặp lượt; không so sánh chéo chuyên khoa và không tự tạo tên.</t>
   </si>
   <si>
     <t>data.summary.sections[order=3].latestBySpecialty[].trends[].from</t>
@@ -2021,16 +2025,12 @@
     <t>Giá trị chỉ số tại lượt trước cùng khoa, giữ đơn vị.</t>
   </si>
   <si>
-    <t>1. Đọc dữ liệu từ: visits[].visit_date; visits[].specialty; visits[].vitals; visits[].labs.paraclinical_result; visits[].labs.abnormal_result
-2. Xử lý:
-Chỉ lấy thông tin 2 trường Huyết áp và Cân nặng  trong visits[].vitals để đi so sánh từ cặp khám gần nhất 
-Và lấy 2 chỉ số visits[].labs.paraclinical_result và visits[].labs.abnormal_result để so sánh chỉ số cần lâm sàn 
-Với mỗi chỉ số có dữ liệu ở cả hai lượt, lấy đúng tên chỉ số từ nguồn làm trend.from. lượt khám gần đây thứ 2 (lượt khám liền trước lượt khám gần nhất)
-Không tự tạo tên chỉ số mới.
-3. Ghi kết quả vào: data.summary.sections[order=3].latestBySpecialty[].trends[].from</t>
-  </si>
-  <si>
-    <t>trends[].from = giá trị của lượt gần đây thứ 2 | Lưu ý: so sánh với lượt gần nhất và chỉ tạo trend khi cả hai lượt có dữ liệu.</t>
+    <t>Xác định lượt đang xét và lượt khám gần nhất trước đó có cùng specialty.
+Với mỗi chỉ số có dữ liệu ở cả hai lượt, lấy giá trị của chỉ số tại lượt trước làm trend.from.
+Giữ nguyên đơn vị và không lấy tên chỉ số làm from.</t>
+  </si>
+  <si>
+    <t>trends[].from = giá trị của chỉ số tại lượt gần nhất trước lượt đang xét và cùng specialty | Lưu ý: giữ nguyên đơn vị; chỉ tạo trend khi cả hai lượt có dữ liệu.</t>
   </si>
   <si>
     <t>data.summary.sections[order=3].latestBySpecialty[].trends[].fromDate</t>
@@ -2039,16 +2039,11 @@
     <t>visit_date của lượt trước cùng khoa.</t>
   </si>
   <si>
-    <t>1. Đọc dữ liệu từ: visits[].visit_date; visits[].specialty; visits[].vitals; visits[].labs.paraclinical_result; visits[].labs.abnormal_result
-2. Xử lý:
-Chỉ lấy thông tin 2 trường Huyết áp và Cân nặng  trong visits[].vitals để đi so sánh từ cặp khám gần nhất 
-Và lấy 2 chỉ số visits[].labs.paraclinical_result và visits[].labs.abnormal_result để so sánh chỉ số cần lâm sàn 
-Với mỗi chỉ số có dữ liệu ở cả hai lượt, lấy đúng tên chỉ số từ nguồn làm trend.fromDate. lượt khám gần đây thứ 2 (lượt khám liền trước lượt khám gần nhất)
-Không tự tạo tên chỉ số mới.
-3. Ghi kết quả vào: data.summary.sections[order=3].latestBySpecialty[].trends[].fromDate</t>
-  </si>
-  <si>
-    <t>trends[].fromDate = visit_date của lượt gần đây thứ 2 | Lưu ý: phải thuộc cặp lượt đang được so sánh.</t>
+    <t>Xác định lượt khám gần nhất trước lượt đang xét và có cùng specialty.
+Lấy visit_date của lượt trước đó làm trend.fromDate.</t>
+  </si>
+  <si>
+    <t>trends[].fromDate = visit_date của lượt gần nhất trước lượt đang xét và cùng specialty | Lưu ý: phải là ngày của đúng lượt cung cấp giá trị trend.from.</t>
   </si>
   <si>
     <t>data.summary.sections[order=3].latestBySpecialty[].trends[].to</t>
@@ -2057,16 +2052,11 @@
     <t>Giá trị cùng chỉ số tại lượt đang xét, giữ đơn vị.</t>
   </si>
   <si>
-    <t>1. Đọc dữ liệu từ: visits[].visit_date; visits[].specialty; visits[].vitals; visits[].labs.paraclinical_result; visits[].labs.abnormal_result
-2. Xử lý:
-Chỉ lấy thông tin 2 trường Huyết áp và Cân nặng  trong visits[].vitals để đi so sánh từ cặp khám gần nhất 
-Và lấy 2 chỉ số visits[].labs.paraclinical_result và visits[].labs.abnormal_result để so sánh chỉ số cần lâm sàn 
-Với mỗi chỉ số có dữ liệu ở cả hai lượt, lấy đúng tên chỉ số từ nguồn làm trend.to( thông số của lượt gần đây nhất )
-Không tự tạo tên chỉ số mới.
-3. Ghi kết quả vào: data.summary.sections[order=3].latestBySpecialty[].trends[].to</t>
-  </si>
-  <si>
-    <t>trends[].to = giá trị của lượt gần nhất | Lưu ý: chỉ tạo trend khi cả hai lượt có dữ liệu.</t>
+    <t>Với mỗi chỉ số có dữ liệu ở cả hai lượt, lấy giá trị của chỉ số tại lượt đang xét làm trend.to.
+Giữ nguyên đơn vị.</t>
+  </si>
+  <si>
+    <t>trends[].to = giá trị của cùng chỉ số tại lượt đang xét | Lưu ý: không mặc định lấy lượt mới nhất toàn bộ visits[].</t>
   </si>
   <si>
     <t>data.summary.sections[order=3].latestBySpecialty[].trends[].toDate</t>
@@ -2075,16 +2065,10 @@
     <t>visit_date của lượt đang xét.</t>
   </si>
   <si>
-    <t>1. Đọc dữ liệu từ: visits[].visit_date; visits[].specialty; visits[].vitals; visits[].labs.paraclinical_result; visits[].labs.abnormal_result
-2. Xử lý:
-Chỉ lấy thông tin 2 trường Huyết áp và Cân nặng  trong visits[].vitals để đi so sánh từ cặp khám gần nhất 
-Và lấy 2 chỉ số visits[].labs.paraclinical_result và visits[].labs.abnormal_result để so sánh chỉ số cần lâm sàn 
-Với mỗi chỉ số có dữ liệu ở cả hai lượt, lấy đúng tên chỉ số từ nguồn làm trend.toDate( thông số của lượt gần đây nhất )
-Không tự tạo tên chỉ số mới.
-3. Ghi kết quả vào: data.summary.sections[order=3].latestBySpecialty[].trends[].toDate</t>
-  </si>
-  <si>
-    <t>trends[].toDate = visit_date của lượt gần nhất | Lưu ý: phải thuộc cặp lượt đang được so sánh.</t>
+    <t>Lấy visit_date của lượt đang xét làm trend.toDate.</t>
+  </si>
+  <si>
+    <t>trends[].toDate = visit_date của lượt đang xét | Lưu ý: phải là ngày của đúng lượt cung cấp giá trị trend.to.</t>
   </si>
   <si>
     <t>data.summary.sections[order=4].followUpItems[]</t>
@@ -2467,17 +2451,19 @@
     <t>Tóm tắt đơn thuốc của chính lượt; giữ tên, liều/cách dùng/thời hạn có ý nghĩa. Đối chiếu plan.prescription cùng lượt khi cần giữ dữ kiện, không tự trộn khác biệt hai nguồn.</t>
   </si>
   <si>
-    <t>1. Đọc dữ liệu từ: visits[].prescriptions[].items[] và visits[].plan.prescription của đúng lượt timeline
-2. Xử lý
+    <t>1. Đọc dữ liệu từ:
+visits[].prescriptions[].items[] của đúng lượt timeline.
+2. Xử lý:
 Tạo một danh sách kết quả rỗng.
-Với mỗi thuốc trong prescriptions[].items[], lấy các trường có giá trị: name, dosage_instruction, duration, route, quantity và note.
-Ghép các giá trị có sẵn thành một chuỗi mô tả thuốc, không tự tạo thêm nội dung, rồi thêm chuỗi đó vào danh sách kết quả.
-Nếu plan.prescription có nội dung hợp lệ và nội dung đó chưa được phản ánh trong danh sách trên thì thêm nguyên văn plan.prescription vào kết quả.
-Loại bỏ nội dung trùng lặp. Nếu cả hai nguồn đều rỗng hoặc không có thông tin thì giữ danh sách rỗng [].
-3. Ghi danh sách kết quả vào: data.timeline[].details.prescription[]</t>
-  </si>
-  <si>
-    <t>data.timeline[].details.prescription[] = ghép prescriptions[].items[] + plan.prescription | Lưu ý: cùng lượt khám; chỉ thêm plan.prescription khi chưa được phản ánh; khử trùng; không có dữ liệu thì [].</t>
+Với mỗi thuốc, lấy các trường có giá trị gồm name, dosage_instruction, duration, route, quantity và note.
+Ghép các giá trị thành một chuỗi mô tả thuốc, không tự tạo thêm nội dung.
+Bỏ nội dung trùng lặp.
+Nếu prescriptions[].items[] rỗng hoặc không có thông tin thì trả [].
+3. Ghi kết quả vào:
+data.timeline[].details.prescription[]</t>
+  </si>
+  <si>
+    <t>timeline[].details.prescription[] = định dạng từng prescriptions[].items[] của đúng lượt khám từ name, dosage_instruction, duration, route, quantity và note | Lưu ý: không sử dụng plan.prescription; bỏ phần rỗng, khử trùng; không có thuốc thì [].</t>
   </si>
   <si>
     <t>Hiện tại chỉ sử phần visits[].prescriptions[] được lấy từ OH thôi ạ</t>
@@ -2702,15 +2688,6 @@
     <t>patient.pseudo_id</t>
   </si>
   <si>
-    <t>1. Đọc dữ liệu từ: patient.pseudo_id
-2. Xử lý:
-Không ánh xạ patient.pseudo_id ra field trực tiếp trong response.
-3. Ghi kết quả vào: Không có field đầu ra trực tiếp</t>
-  </si>
-  <si>
-    <t>Không có field đầu ra trực tiếp = patient.pseudo_id | Lưu ý: Không ánh xạ patient.pseudo_id ra field trực tiếp trong response.</t>
-  </si>
-  <si>
     <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.5 — input
   "patient": { "pseudoId": "1ae82d07...70d8", "age": 79, "gender": "male" },
 Nguồn: PRD Patient Summary.docx — Phần II, Phụ lục D — kiểm tra dữ liệu
@@ -2718,15 +2695,6 @@
 Nguồn: PRD Patient Summary.docx — Phần II, mục 5
 Payload dưới đây là template cấu trúc response đã chốt. Giá trị chỉ để minh họa và không phải expected output của input tại mục 2.5. Không bổ sung field ngoài contract.
 Ghi chú đối chiếu (không phải trích dẫn PRD): pseudoId có trong input, không có field trả trực tiếp tương ứng trong response mục 5.</t>
-  </si>
-  <si>
-    <t>1. Đọc dữ liệu từ: visits[].clinic
-2. Xử lý:
-Không ánh xạ visits[].clinic ra field trực tiếp trong response.
-3. Ghi kết quả vào: Không có field đầu ra trực tiếp</t>
-  </si>
-  <si>
-    <t>Không có field đầu ra trực tiếp = visits[].clinic | Lưu ý: Không ánh xạ visits[].clinic ra field trực tiếp trong response.</t>
   </si>
   <si>
     <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.2
@@ -2744,21 +2712,6 @@
     <t>visits[].history.current_medications[].last_dose_date</t>
   </si>
   <si>
-    <t>1. Đọc dữ liệu từ: visits[].history.current_medications[].last_dose_date
-2. Xử lý:
-Không ánh xạ current_medications[].last_dose_date ra field trực tiếp trong response.
-3. Ghi kết quả vào: Không có field đầu ra trực tiếp</t>
-  </si>
-  <si>
-    <t>1. Đọc dữ liệu từ: visits[].prescriptions[].prescriber
-2. Xử lý:
-Không ánh xạ prescriptions[].prescriber ra field trực tiếp trong response.
-3. Ghi kết quả vào: Không có field đầu ra trực tiếp</t>
-  </si>
-  <si>
-    <t>Không có field đầu ra trực tiếp = visits[].prescriptions[].prescriber | Lưu ý: Không ánh xạ prescriptions[].prescriber ra field trực tiếp trong response.</t>
-  </si>
-  <si>
     <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.4
 prescriber
 Bác sĩ kê đơn
@@ -2772,16 +2725,6 @@
     <t>visits[].prescriptions[].diagnosis_on_prescription</t>
   </si>
   <si>
-    <t>1. Đọc dữ liệu từ: visits[].prescriptions[].diagnosis_on_prescription
-2. Xử lý:
-THEO XÁC NHẬN DEV: dùng làm nguồn gián tiếp cho oneLiner, nội dung Tiền sử nền và timeline.
-Lưu ý: PRD không quy định field output trực tiếp cho nguồn này, nên không tạo output riêng.
-3. Ghi gián tiếp vào ngữ cảnh của: data.summary.oneLiner; data.summary.sections[order=1].items[].content; data.timeline[].summary</t>
-  </si>
-  <si>
-    <t>Không có field đầu ra trực tiếp = visits[].prescriptions[].diagnosis_on_prescription | Lưu ý: THEO XÁC NHẬN DEV: dùng làm nguồn gián tiếp cho oneLiner, nội dung Tiền sử nền và timeline. Lưu ý: PRD không quy định field output trực tiếp cho nguồn này, nên không tạo output riêng.</t>
-  </si>
-  <si>
     <t>Vẫn sử dụng trong đầu vào của oneliner, Tiền sử nền, Timeline</t>
   </si>
   <si>
@@ -2802,17 +2745,6 @@
   </si>
   <si>
     <t>visits[].prescriptions[].items[].stop_date</t>
-  </si>
-  <si>
-    <t>1. Đọc dữ liệu từ: visits[].prescriptions[].items[].stop_date
-2. Xử lý:
-THEO XÁC NHẬN DEV: dùng stop_date để xác định thuốc còn hạn và hỗ trợ chọn thuốc/lượt khám.
-Lưu ý: PRD cũ chưa mô tả rõ quy tắc này.
-Không tạo field output riêng ở dòng này; durationEndDate đã được map tại No.27.
-3. Kết quả: dùng nội bộ cho điều kiện chọn dữ liệu</t>
-  </si>
-  <si>
-    <t>Không có field đầu ra trực tiếp = chọn/lọc(visits[].prescriptions[].items[].stop_date) | Lưu ý: THEO XÁC NHẬN DEV: dùng stop_date để xác định thuốc còn hạn và hỗ trợ chọn thuốc/lượt khám. Lưu ý: PRD cũ chưa mô tả rõ quy tắc này. Không tạo field output riêng ở dòng này; durationEndDate đã được map tại No.27.</t>
   </si>
   <si>
     <t>Có dùng để xét thuốc đó hết hạn chưa</t>
@@ -7167,7 +7099,7 @@
   <dimension ref="A1:N100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.85185185185185" style="16" customWidth="1"/>
+    <col min="1" max="1" width="14.6018518518519" style="16" customWidth="1"/>
     <col min="2" max="2" width="73.3240740740741" style="16" customWidth="1"/>
     <col min="3" max="3" width="18.712962962963" style="16" customWidth="1"/>
     <col min="4" max="4" width="50" style="16" customWidth="1"/>
@@ -10609,12 +10541,8 @@
         <v>173</v>
       </c>
       <c r="F91" s="23"/>
-      <c r="G91" s="24" t="s">
-        <v>620</v>
-      </c>
-      <c r="H91" s="24" t="s">
-        <v>621</v>
-      </c>
+      <c r="G91" s="24"/>
+      <c r="H91" s="24"/>
       <c r="I91" s="26" t="s">
         <v>178</v>
       </c>
@@ -10625,7 +10553,7 @@
         <v>179</v>
       </c>
       <c r="L91" s="26" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="92" ht="351" customHeight="1" spans="1:14">
@@ -10645,12 +10573,8 @@
         <v>173</v>
       </c>
       <c r="F92" s="23"/>
-      <c r="G92" s="24" t="s">
-        <v>623</v>
-      </c>
-      <c r="H92" s="24" t="s">
-        <v>624</v>
-      </c>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
       <c r="I92" s="26" t="s">
         <v>178</v>
       </c>
@@ -10661,7 +10585,7 @@
         <v>179</v>
       </c>
       <c r="L92" s="26" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="93" ht="76.5" customHeight="1" spans="1:14">
@@ -10675,15 +10599,13 @@
         <v>241</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="E93" s="23" t="s">
         <v>190</v>
       </c>
       <c r="F93" s="23"/>
-      <c r="G93" s="24" t="s">
-        <v>627</v>
-      </c>
+      <c r="G93" s="24"/>
       <c r="H93" s="24"/>
       <c r="I93" s="26" t="s">
         <v>178</v>
@@ -10715,12 +10637,8 @@
         <v>173</v>
       </c>
       <c r="F94" s="23"/>
-      <c r="G94" s="24" t="s">
-        <v>628</v>
-      </c>
-      <c r="H94" s="24" t="s">
-        <v>629</v>
-      </c>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
       <c r="I94" s="26" t="s">
         <v>178</v>
       </c>
@@ -10731,7 +10649,7 @@
         <v>179</v>
       </c>
       <c r="L94" s="26" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
     </row>
     <row r="95" ht="259.5" customHeight="1" spans="1:14">
@@ -10745,20 +10663,16 @@
         <v>241</v>
       </c>
       <c r="D95" s="23" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="E95" s="23" t="s">
         <v>173</v>
       </c>
       <c r="F95" s="23"/>
-      <c r="G95" s="24" t="s">
-        <v>632</v>
-      </c>
-      <c r="H95" s="24" t="s">
-        <v>633</v>
-      </c>
+      <c r="G95" s="24"/>
+      <c r="H95" s="24"/>
       <c r="I95" s="26" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="J95" s="23" t="s">
         <v>179</v>
@@ -10767,13 +10681,13 @@
         <v>179</v>
       </c>
       <c r="L95" s="26" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="M95" s="40" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="N95" s="49" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
     </row>
     <row r="96" ht="229.5" customHeight="1" spans="1:14">
@@ -10787,20 +10701,16 @@
         <v>241</v>
       </c>
       <c r="D96" s="23" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="E96" s="23" t="s">
         <v>173</v>
       </c>
       <c r="F96" s="23"/>
-      <c r="G96" s="24" t="s">
-        <v>639</v>
-      </c>
-      <c r="H96" s="24" t="s">
-        <v>640</v>
-      </c>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
       <c r="I96" s="26" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="J96" s="23" t="s">
         <v>179</v>
@@ -10809,10 +10719,10 @@
         <v>179</v>
       </c>
       <c r="L96" s="26" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="M96" s="38" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="N96" s="38"/>
     </row>
@@ -10834,22 +10744,22 @@
       <c r="G97" s="24"/>
       <c r="H97" s="24"/>
       <c r="I97" s="26" t="s">
+        <v>625</v>
+      </c>
+      <c r="J97" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="K97" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="L97" s="26" t="s">
+        <v>633</v>
+      </c>
+      <c r="M97" s="40" t="s">
+        <v>627</v>
+      </c>
+      <c r="N97" s="38" t="s">
         <v>634</v>
-      </c>
-      <c r="J97" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="K97" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="L97" s="26" t="s">
-        <v>644</v>
-      </c>
-      <c r="M97" s="40" t="s">
-        <v>636</v>
-      </c>
-      <c r="N97" s="38" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="98" ht="409.5" customHeight="1" spans="1:14">
@@ -10857,25 +10767,25 @@
         <v>97</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="C98" s="23" t="s">
         <v>241</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="E98" s="23" t="s">
         <v>173</v>
       </c>
       <c r="F98" s="23" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="I98" s="26" t="s">
         <v>178</v>
@@ -10887,7 +10797,7 @@
         <v>179</v>
       </c>
       <c r="L98" s="26" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
     </row>
     <row r="99" ht="409.5" customHeight="1" spans="1:14">
@@ -10895,25 +10805,25 @@
         <v>98</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="C99" s="23" t="s">
         <v>241</v>
       </c>
       <c r="D99" s="23" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="E99" s="23" t="s">
         <v>173</v>
       </c>
       <c r="F99" s="23" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="G99" s="24" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="I99" s="26" t="s">
         <v>178</v>
@@ -10925,7 +10835,7 @@
         <v>179</v>
       </c>
       <c r="L99" s="26" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -10963,512 +10873,512 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="13" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="13" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="13" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
     </row>
   </sheetData>
@@ -11489,1458 +11399,1458 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>775</v>
+        <v>764</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>786</v>
+        <v>775</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>788</v>
+        <v>777</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>794</v>
+        <v>783</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>799</v>
+        <v>788</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>806</v>
+        <v>795</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>807</v>
+        <v>796</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>808</v>
+        <v>797</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>810</v>
+        <v>799</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>813</v>
+        <v>802</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>814</v>
+        <v>803</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>820</v>
+        <v>809</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>821</v>
+        <v>810</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>822</v>
+        <v>811</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>823</v>
+        <v>812</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>824</v>
+        <v>813</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>825</v>
+        <v>814</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>826</v>
+        <v>815</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>827</v>
+        <v>816</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>828</v>
+        <v>817</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>830</v>
+        <v>819</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>831</v>
+        <v>820</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>835</v>
+        <v>824</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>836</v>
+        <v>825</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>838</v>
+        <v>827</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>821</v>
+        <v>810</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>846</v>
+        <v>835</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>849</v>
+        <v>838</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>850</v>
+        <v>839</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>851</v>
+        <v>840</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>855</v>
+        <v>844</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>856</v>
+        <v>845</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>857</v>
+        <v>846</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>858</v>
+        <v>847</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>859</v>
+        <v>848</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>860</v>
+        <v>849</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>861</v>
+        <v>850</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>862</v>
+        <v>851</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>863</v>
+        <v>852</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>864</v>
+        <v>853</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>865</v>
+        <v>854</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>866</v>
+        <v>855</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>868</v>
+        <v>857</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>869</v>
+        <v>858</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>870</v>
+        <v>859</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>871</v>
+        <v>860</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>875</v>
+        <v>864</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>876</v>
+        <v>865</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>877</v>
+        <v>866</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>879</v>
+        <v>868</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>860</v>
+        <v>849</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>861</v>
+        <v>850</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>880</v>
+        <v>869</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>881</v>
+        <v>870</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>885</v>
+        <v>874</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>886</v>
+        <v>875</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>879</v>
+        <v>868</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>895</v>
+        <v>884</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>879</v>
+        <v>868</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>900</v>
+        <v>889</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>901</v>
+        <v>890</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>901</v>
+        <v>890</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>912</v>
+        <v>901</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>916</v>
+        <v>905</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>879</v>
+        <v>868</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>917</v>
+        <v>906</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>918</v>
+        <v>907</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>919</v>
+        <v>908</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>920</v>
+        <v>909</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>921</v>
+        <v>910</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>924</v>
+        <v>913</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>925</v>
+        <v>914</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>821</v>
+        <v>810</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>927</v>
+        <v>916</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>928</v>
+        <v>917</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>931</v>
+        <v>920</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>934</v>
+        <v>923</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>935</v>
+        <v>924</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>936</v>
+        <v>925</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>937</v>
+        <v>926</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>940</v>
+        <v>929</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>941</v>
+        <v>930</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>942</v>
+        <v>931</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>943</v>
+        <v>932</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>944</v>
+        <v>933</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>945</v>
+        <v>934</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>946</v>
+        <v>935</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>947</v>
+        <v>936</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>948</v>
+        <v>937</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>949</v>
+        <v>938</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>950</v>
+        <v>939</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>951</v>
+        <v>940</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>952</v>
+        <v>941</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>954</v>
+        <v>943</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>955</v>
+        <v>944</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>956</v>
+        <v>945</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>958</v>
+        <v>947</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>959</v>
+        <v>948</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>960</v>
+        <v>949</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>961</v>
+        <v>950</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>962</v>
+        <v>951</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>973</v>
+        <v>962</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>974</v>
+        <v>963</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>976</v>
+        <v>965</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>982</v>
+        <v>971</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>983</v>
+        <v>972</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>985</v>
+        <v>974</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>987</v>
+        <v>976</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>989</v>
+        <v>978</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>992</v>
+        <v>981</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>993</v>
+        <v>982</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>994</v>
+        <v>983</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>995</v>
+        <v>984</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>997</v>
+        <v>986</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
     </row>
   </sheetData>
@@ -12957,1512 +12867,1512 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="7" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>998</v>
+        <v>987</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="7" t="s">
-        <v>999</v>
+        <v>988</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="7" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="7" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="7" t="s">
-        <v>1002</v>
+        <v>991</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="7" t="s">
-        <v>1003</v>
+        <v>992</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="7" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="7" t="s">
-        <v>1005</v>
+        <v>994</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="7" t="s">
-        <v>1006</v>
+        <v>995</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="7" t="s">
-        <v>1007</v>
+        <v>996</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="7" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="7" t="s">
-        <v>1009</v>
+        <v>998</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="7" t="s">
-        <v>1010</v>
+        <v>999</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="7" t="s">
-        <v>1011</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="7" t="s">
-        <v>1012</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="7" t="s">
-        <v>1013</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="7" t="s">
-        <v>1014</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="7" t="s">
-        <v>1015</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="7" t="s">
-        <v>1016</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="7" t="s">
-        <v>1018</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="7" t="s">
-        <v>1019</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="7" t="s">
-        <v>1020</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="7" t="s">
-        <v>1021</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="7" t="s">
-        <v>1022</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="7" t="s">
-        <v>1023</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="7" t="s">
-        <v>1024</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="7" t="s">
-        <v>1026</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="7" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="7" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="8" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="7" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="7" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="8" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="8" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="7" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="7" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="7" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="7" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="7" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="8" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="8" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="8" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="8" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="7" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="7" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="7" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="7" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="8" t="s">
-        <v>1047</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="7" t="s">
-        <v>1048</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="7" t="s">
-        <v>1049</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="7" t="s">
-        <v>1050</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="8" t="s">
-        <v>1051</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="7" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="7" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="7" t="s">
-        <v>1052</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="7" t="s">
-        <v>1053</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="7" t="s">
-        <v>1054</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="7" t="s">
-        <v>1055</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="7" t="s">
-        <v>1056</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="7" t="s">
-        <v>1057</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="8" t="s">
-        <v>1058</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="7" t="s">
-        <v>1059</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="7" t="s">
-        <v>1060</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="7" t="s">
-        <v>1061</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="7" t="s">
-        <v>1062</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="7" t="s">
-        <v>1063</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="7" t="s">
-        <v>1064</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="7" t="s">
-        <v>1065</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="7" t="s">
-        <v>1066</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="7" t="s">
-        <v>1067</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="7" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="7" t="s">
-        <v>1068</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="7" t="s">
-        <v>1069</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="7" t="s">
-        <v>1070</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="7" t="s">
-        <v>1071</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="7" t="s">
-        <v>1072</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="9" t="s">
-        <v>1073</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="7" t="s">
-        <v>1074</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="7" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="7" t="s">
-        <v>1075</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="7" t="s">
-        <v>1076</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="7" t="s">
-        <v>1077</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="7" t="s">
-        <v>1078</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="7" t="s">
-        <v>995</v>
+        <v>984</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="7" t="s">
-        <v>1002</v>
+        <v>991</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="7" t="s">
-        <v>1079</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="7" t="s">
-        <v>1080</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="7" t="s">
-        <v>1081</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="7" t="s">
-        <v>1082</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="7" t="s">
-        <v>1083</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="7" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="7" t="s">
-        <v>1009</v>
+        <v>998</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="7" t="s">
-        <v>1084</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="7" t="s">
-        <v>1085</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="7" t="s">
-        <v>1086</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="7" t="s">
-        <v>1013</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="7" t="s">
-        <v>1014</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="7" t="s">
-        <v>1087</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="7" t="s">
-        <v>1088</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="7" t="s">
-        <v>1018</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="7" t="s">
-        <v>1089</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="7" t="s">
-        <v>1090</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="8" t="s">
-        <v>1021</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="7" t="s">
-        <v>1091</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="7" t="s">
-        <v>1023</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="7" t="s">
-        <v>1024</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="7" t="s">
-        <v>1092</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="7" t="s">
-        <v>1093</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="7" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="8" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="7" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="7" t="s">
-        <v>1095</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="7" t="s">
-        <v>1096</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="7" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="8" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="7" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="7" t="s">
-        <v>1026</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="7" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="7" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="8" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="7" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="7" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="8" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="8" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="7" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="7" t="s">
-        <v>1097</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="7" t="s">
-        <v>1098</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="7" t="s">
-        <v>1099</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="7" t="s">
-        <v>1100</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="8" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="8" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="8" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="8" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="7" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="7" t="s">
-        <v>1101</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="7" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="7" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="7" t="s">
-        <v>1047</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="7" t="s">
-        <v>1048</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="7" t="s">
-        <v>1102</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="7" t="s">
-        <v>1103</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="8" t="s">
-        <v>1051</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="7" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="7" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="7" t="s">
-        <v>1104</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="7" t="s">
-        <v>1049</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="7" t="s">
-        <v>1050</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="8" t="s">
-        <v>1051</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="7" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="7" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="7" t="s">
-        <v>1105</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="7" t="s">
-        <v>1054</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="7" t="s">
-        <v>1055</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="7" t="s">
-        <v>1106</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="7" t="s">
-        <v>1107</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="8" t="s">
-        <v>1058</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="7" t="s">
-        <v>1059</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="7" t="s">
-        <v>1060</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="7" t="s">
-        <v>1108</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="7" t="s">
-        <v>1109</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="7" t="s">
-        <v>1110</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="7" t="s">
-        <v>1111</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" s="7" t="s">
-        <v>1112</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="8" t="s">
-        <v>1066</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="7" t="s">
-        <v>1067</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="7" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="7" t="s">
-        <v>1113</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="7" t="s">
-        <v>1114</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="7" t="s">
-        <v>1070</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="7" t="s">
-        <v>1115</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="7" t="s">
-        <v>1116</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="8" t="s">
-        <v>1073</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="7" t="s">
-        <v>1074</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="7" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="7" t="s">
-        <v>1075</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="7" t="s">
-        <v>1076</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="7" t="s">
-        <v>1077</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="7" t="s">
-        <v>1078</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="7" t="s">
-        <v>995</v>
+        <v>984</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" s="7" t="s">
-        <v>1002</v>
+        <v>991</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="7" t="s">
-        <v>1117</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="7" t="s">
-        <v>1118</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="7" t="s">
-        <v>1119</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="7" t="s">
-        <v>1120</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="7" t="s">
-        <v>1121</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="7" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="7" t="s">
-        <v>1122</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="7" t="s">
-        <v>1123</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="7" t="s">
-        <v>1124</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" s="7" t="s">
-        <v>1012</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="7" t="s">
-        <v>1125</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="7" t="s">
-        <v>1014</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="7" t="s">
-        <v>1126</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="7" t="s">
-        <v>1088</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="7" t="s">
-        <v>1018</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="7" t="s">
-        <v>1127</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="7" t="s">
-        <v>1128</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="8" t="s">
-        <v>1021</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="7" t="s">
-        <v>1129</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="7" t="s">
-        <v>1023</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="7" t="s">
-        <v>1024</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="7" t="s">
-        <v>1095</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="7" t="s">
-        <v>1096</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="7" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="8" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" s="7" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="7" t="s">
-        <v>1130</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="7" t="s">
-        <v>1131</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="7" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="8" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="7" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="7" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="7" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" s="7" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="7" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="7" t="s">
-        <v>1132</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" s="7" t="s">
-        <v>1133</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" s="7" t="s">
-        <v>1134</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" s="7" t="s">
-        <v>1100</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="8" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="8" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="8" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="8" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="7" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="7" t="s">
-        <v>1135</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="7" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="7" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" s="7" t="s">
-        <v>1047</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="7" t="s">
-        <v>1048</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" s="7" t="s">
-        <v>1136</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="7" t="s">
-        <v>1137</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="8" t="s">
-        <v>1051</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" s="7" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="7" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" s="7" t="s">
-        <v>1104</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="7" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="7" t="s">
-        <v>1102</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="7" t="s">
-        <v>1103</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="8" t="s">
-        <v>1051</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="7" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="7" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="7" t="s">
-        <v>1138</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="7" t="s">
-        <v>1054</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="7" t="s">
-        <v>1139</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="7" t="s">
-        <v>1140</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="7" t="s">
-        <v>1141</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" s="8" t="s">
-        <v>1058</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="7" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="7" t="s">
-        <v>1059</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="7" t="s">
-        <v>1060</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="7" t="s">
-        <v>1142</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="7" t="s">
-        <v>1143</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="7" t="s">
-        <v>1144</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="7" t="s">
-        <v>1145</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="7" t="s">
-        <v>1146</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="7" t="s">
-        <v>1066</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" s="7" t="s">
-        <v>1067</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="7" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="7" t="s">
-        <v>1147</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="7" t="s">
-        <v>1148</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="7" t="s">
-        <v>1070</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="7" t="s">
-        <v>1149</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="7" t="s">
-        <v>1150</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="8" t="s">
-        <v>1073</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="8" t="s">
-        <v>1074</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" s="7" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="7" t="s">
-        <v>1075</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" s="7" t="s">
-        <v>1076</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" s="7" t="s">
-        <v>1077</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" s="7" t="s">
-        <v>1078</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" s="7" t="s">
-        <v>1151</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" s="7" t="s">
-        <v>1152</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" s="7" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" s="7" t="s">
-        <v>1153</v>
+        <v>1142</v>
       </c>
     </row>
   </sheetData>
@@ -14492,31 +14402,31 @@
   <sheetData>
     <row r="1" ht="43.5" customHeight="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>1154</v>
+        <v>1143</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1155</v>
+        <v>1144</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1156</v>
+        <v>1145</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1157</v>
+        <v>1146</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1158</v>
+        <v>1147</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1159</v>
+        <v>1148</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>168</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1160</v>
+        <v>1149</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1161</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="2" ht="43.5" customHeight="1" spans="1:10">
@@ -14527,7 +14437,7 @@
         <v>174</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1162</v>
+        <v>1151</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>11</v>
@@ -14545,7 +14455,7 @@
         <v>11</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1163</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="3" ht="28.5" customHeight="1" spans="1:10">
@@ -14553,10 +14463,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1164</v>
+        <v>1153</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1165</v>
+        <v>1154</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
@@ -14571,7 +14481,7 @@
         <v>179</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1166</v>
+        <v>1155</v>
       </c>
       <c r="I3" s="3"/>
     </row>
@@ -14589,19 +14499,19 @@
         <v>11</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1167</v>
+        <v>1156</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1167</v>
+        <v>1156</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>179</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>1167</v>
+        <v>1156</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>1168</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="5" ht="57.75" customHeight="1" spans="1:10">
@@ -14609,7 +14519,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>173</v>
@@ -14621,16 +14531,16 @@
         <v>208</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1169</v>
+        <v>1158</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1170</v>
+        <v>1159</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>1171</v>
+        <v>1160</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -14639,7 +14549,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>173</v>
@@ -14651,16 +14561,16 @@
         <v>208</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>179</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1170</v>
+        <v>1159</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>1171</v>
+        <v>1160</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -14681,16 +14591,16 @@
         <v>208</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1172</v>
+        <v>1161</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>179</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1173</v>
+        <v>1162</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1174</v>
+        <v>1163</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -14702,7 +14612,7 @@
         <v>291</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1165</v>
+        <v>1154</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>11</v>
@@ -14711,16 +14621,16 @@
         <v>208</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1175</v>
+        <v>1164</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>179</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1176</v>
+        <v>1165</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>1177</v>
+        <v>1166</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -14729,7 +14639,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>173</v>
@@ -14741,16 +14651,16 @@
         <v>208</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1178</v>
+        <v>1167</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>208</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1179</v>
+        <v>1168</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>1180</v>
+        <v>1169</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -14759,7 +14669,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1181</v>
+        <v>1170</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>173</v>
@@ -14777,7 +14687,7 @@
         <v>208</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1182</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="11" ht="28.5" customHeight="1" spans="1:10">
@@ -14797,13 +14707,13 @@
         <v>208</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1183</v>
+        <v>1172</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>179</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1184</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -14829,7 +14739,7 @@
         <v>179</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1185</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:10">
@@ -14837,7 +14747,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1186</v>
+        <v>1175</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>173</v>
@@ -14849,13 +14759,13 @@
         <v>208</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>1187</v>
+        <v>1176</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>179</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1188</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="14" ht="28.5" customHeight="1" spans="1:10">
@@ -14881,7 +14791,7 @@
         <v>179</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1189</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="15" ht="28.5" customHeight="1" spans="1:10">
@@ -14889,7 +14799,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1190</v>
+        <v>1179</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>173</v>
@@ -14907,7 +14817,7 @@
         <v>179</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1191</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="16" ht="164.25" customHeight="1" spans="1:10">
@@ -14915,10 +14825,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1165</v>
+        <v>1154</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>11</v>
@@ -14933,10 +14843,10 @@
         <v>179</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>1192</v>
+        <v>1181</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1193</v>
+        <v>1182</v>
       </c>
       <c r="J16" s="6"/>
     </row>
@@ -14945,7 +14855,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1194</v>
+        <v>1183</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>173</v>
@@ -14963,7 +14873,7 @@
         <v>179</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>1195</v>
+        <v>1184</v>
       </c>
       <c r="I17" s="3"/>
     </row>
@@ -14972,7 +14882,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1196</v>
+        <v>1185</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>173</v>
@@ -14984,13 +14894,13 @@
         <v>208</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1197</v>
+        <v>1186</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>208</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1198</v>
+        <v>1187</v>
       </c>
       <c r="I18" s="3"/>
     </row>
@@ -15015,657 +14925,657 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="B2" t="s">
-        <v>1199</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="C3" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="D4" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="D5" t="s">
-        <v>1201</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="D6" t="s">
-        <v>1202</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="D7" t="s">
-        <v>1203</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="D8" t="s">
-        <v>1204</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="D9" t="s">
-        <v>1205</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="D10" t="s">
-        <v>1206</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="D11" t="s">
-        <v>1207</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="D12" t="s">
-        <v>1208</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="D13" t="s">
-        <v>1209</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="D14" t="s">
-        <v>1210</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="D15" t="s">
-        <v>1211</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="D16" t="s">
-        <v>1212</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>1213</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>1214</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>1215</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>1216</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>1217</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>1218</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>1219</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>1220</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="25" spans="4:4">
       <c r="D25" t="s">
-        <v>1221</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="26" spans="4:4">
       <c r="D26" t="s">
-        <v>1222</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="27" spans="4:4">
       <c r="D27" t="s">
-        <v>1223</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="28" spans="4:4">
       <c r="D28" t="s">
-        <v>1224</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="29" spans="4:4">
       <c r="D29" t="s">
-        <v>1225</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="30" spans="4:4">
       <c r="D30" t="s">
-        <v>1226</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="31" spans="4:4">
       <c r="D31" t="s">
-        <v>1227</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="32" spans="4:4">
       <c r="D32" t="s">
-        <v>1228</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="D33" t="s">
-        <v>1229</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="D34" t="s">
-        <v>1230</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="D35" t="s">
-        <v>1231</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="D36" t="s">
-        <v>1232</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="D37" t="s">
-        <v>1233</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="D38" t="s">
-        <v>1234</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="D39" t="s">
-        <v>1235</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="D40" t="s">
-        <v>1236</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="D41" t="s">
-        <v>1237</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="D42" t="s">
-        <v>1238</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="D43" t="s">
-        <v>1239</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="D44" t="s">
-        <v>1240</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="D45" t="s">
-        <v>1241</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="D46" t="s">
-        <v>1242</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="47" spans="2:4">
       <c r="C47" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
     </row>
     <row r="48" spans="2:4">
       <c r="B48" t="s">
-        <v>1243</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="49" spans="2:4">
       <c r="B49" t="s">
-        <v>1244</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="50" spans="2:4">
       <c r="C50" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
     </row>
     <row r="51" spans="2:4">
       <c r="D51" t="s">
-        <v>1245</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="52" spans="2:4">
       <c r="D52" t="s">
-        <v>1246</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="53" spans="2:4">
       <c r="D53" t="s">
-        <v>1247</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="54" spans="2:4">
       <c r="D54" t="s">
-        <v>1248</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="55" spans="2:4">
       <c r="D55" t="s">
-        <v>1249</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="56" spans="2:4">
       <c r="D56" t="s">
-        <v>1250</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="57" spans="2:4">
       <c r="D57" t="s">
-        <v>1251</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="58" spans="2:4">
       <c r="D58" t="s">
-        <v>1252</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="59" spans="2:4">
       <c r="D59" t="s">
-        <v>1253</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="60" spans="2:4">
       <c r="D60" t="s">
-        <v>1254</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="61" spans="2:4">
       <c r="D61" t="s">
-        <v>1255</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="62" spans="2:4">
       <c r="C62" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
     </row>
     <row r="63" spans="2:4">
       <c r="B63" t="s">
-        <v>1243</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="64" spans="2:4">
       <c r="B64" t="s">
-        <v>1256</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="65" spans="3:4">
       <c r="C65" t="s">
-        <v>1257</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="66" spans="3:4">
       <c r="C66" t="s">
-        <v>1258</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="67" spans="3:4">
       <c r="C67" t="s">
-        <v>1259</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="68" spans="3:4">
       <c r="C68" t="s">
-        <v>1260</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="69" spans="3:4">
       <c r="C69" t="s">
-        <v>1261</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="C70" t="s">
-        <v>1262</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="71" spans="3:4">
       <c r="D71" t="s">
-        <v>1263</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="72" spans="3:4">
       <c r="D72" t="s">
-        <v>1264</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="73" spans="3:4">
       <c r="D73" t="s">
-        <v>1252</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="74" spans="3:4">
       <c r="D74" t="s">
-        <v>1265</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="75" spans="3:4">
       <c r="D75" t="s">
-        <v>1254</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="76" spans="3:4">
       <c r="D76" t="s">
-        <v>1249</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="77" spans="3:4">
       <c r="D77" t="s">
-        <v>1251</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="78" spans="3:4">
       <c r="D78" t="s">
-        <v>1250</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="79" spans="3:4">
       <c r="D79" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="80" spans="3:4">
       <c r="D80" t="s">
-        <v>1267</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="81" spans="4:4">
       <c r="D81" t="s">
-        <v>1268</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="82" spans="4:4">
       <c r="D82" t="s">
-        <v>1269</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="83" spans="4:4">
       <c r="D83" t="s">
-        <v>1270</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="84" spans="4:4">
       <c r="D84" t="s">
-        <v>1271</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="85" spans="4:4">
       <c r="D85" t="s">
-        <v>1272</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="86" spans="4:4">
       <c r="D86" t="s">
-        <v>1273</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="87" spans="4:4">
       <c r="D87" t="s">
-        <v>1274</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="88" spans="4:4">
       <c r="D88" t="s">
-        <v>1275</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="89" spans="4:4">
       <c r="D89" t="s">
-        <v>1276</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="90" spans="4:4">
       <c r="D90" t="s">
-        <v>1277</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="91" spans="4:4">
       <c r="D91" t="s">
-        <v>1278</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="92" spans="4:4">
       <c r="D92" t="s">
-        <v>1279</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="93" spans="4:4">
       <c r="D93" t="s">
-        <v>1280</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="94" spans="4:4">
       <c r="D94" t="s">
-        <v>1281</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="95" spans="4:4">
       <c r="D95" t="s">
-        <v>1282</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="96" spans="4:4">
       <c r="D96" t="s">
-        <v>1283</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="97" spans="3:5">
       <c r="D97" t="s">
-        <v>1284</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="98" spans="3:5">
       <c r="D98" t="s">
-        <v>1285</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="99" spans="3:5">
       <c r="C99" t="s">
-        <v>1286</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="100" spans="3:5">
       <c r="C100" t="s">
-        <v>1287</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="101" spans="3:5">
       <c r="D101" t="s">
-        <v>1288</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="102" spans="3:5">
       <c r="D102" t="s">
-        <v>1289</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="103" spans="3:5">
       <c r="D103" t="s">
-        <v>1290</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="104" spans="3:5">
       <c r="D104" t="s">
-        <v>1291</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="105" spans="3:5">
       <c r="D105" t="s">
-        <v>1292</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="106" spans="3:5">
       <c r="D106" t="s">
-        <v>1293</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="107" spans="3:5">
       <c r="D107" t="s">
-        <v>1294</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="108" spans="3:5">
       <c r="D108" t="s">
-        <v>1295</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="109" spans="3:5">
       <c r="D109" t="s">
-        <v>1296</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="110" spans="3:5">
       <c r="E110" t="s">
-        <v>1297</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="111" spans="3:5">
       <c r="E111" t="s">
-        <v>1298</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="112" spans="3:5">
       <c r="E112" t="s">
-        <v>1299</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="113" spans="3:5">
       <c r="E113" t="s">
-        <v>1300</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="114" spans="3:5">
       <c r="E114" t="s">
-        <v>1301</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="115" spans="3:5">
       <c r="E115" t="s">
-        <v>1302</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="116" spans="3:5">
       <c r="E116" t="s">
-        <v>1303</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="117" spans="3:5">
       <c r="E117" t="s">
-        <v>1304</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="118" spans="3:5">
       <c r="D118" t="s">
-        <v>1286</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="119" spans="3:5">
       <c r="D119" t="s">
-        <v>1305</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="120" spans="3:5">
       <c r="D120" t="s">
-        <v>1306</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="121" spans="3:5">
       <c r="D121" t="s">
-        <v>1307</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="122" spans="3:5">
       <c r="C122" t="s">
-        <v>1286</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="123" spans="3:5">
       <c r="C123" t="s">
-        <v>1308</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="124" spans="3:5">
       <c r="C124" t="s">
-        <v>1309</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="125" spans="3:5">
       <c r="C125" t="s">
-        <v>1310</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="126" spans="3:5">
       <c r="C126" t="s">
-        <v>1311</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="127" spans="3:5">
       <c r="C127" t="s">
-        <v>1207</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="128" spans="3:5">
       <c r="C128" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="B129" t="s">
-        <v>1286</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="B130" t="s">
-        <v>1313</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
     </row>
   </sheetData>

--- a/Dữ liệu mẫu/Mapping.xlsx
+++ b/Dữ liệu mẫu/Mapping.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping data&lt;-&gt;req by QC'!$A$1:$E$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping req&lt;-&gt;res by QC'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping req&lt;-&gt;res by QC'!$A$1:$P$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Request fields unmapped'!$A$1:$I$18</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2801,7 +2801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.6018518518519" customWidth="1" style="16" min="1" max="1"/>
@@ -2812,13 +2812,14 @@
     <col width="36.4259259259259" customWidth="1" style="16" min="6" max="6"/>
     <col width="75" customWidth="1" style="16" min="7" max="8"/>
     <col width="72" customWidth="1" style="16" min="9" max="9"/>
-    <col width="12.287037037037" customWidth="1" style="16" min="10" max="10"/>
-    <col width="53.5740740740741" customWidth="1" style="16" min="11" max="11"/>
-    <col width="41.5740740740741" customWidth="1" style="16" min="12" max="12"/>
-    <col width="62" customWidth="1" style="16" min="13" max="13"/>
-    <col width="9.138888888888889" customWidth="1" style="16" min="14" max="14"/>
-    <col width="33.4907407407407" customWidth="1" style="16" min="15" max="16384"/>
-    <col width="9.138888888888889" customWidth="1" min="16" max="16"/>
+    <col width="68" customWidth="1" style="16" min="10" max="10"/>
+    <col width="12.287037037037" customWidth="1" style="16" min="11" max="11"/>
+    <col width="53.5740740740741" customWidth="1" style="16" min="12" max="12"/>
+    <col width="41.5740740740741" customWidth="1" style="16" min="13" max="13"/>
+    <col width="62" customWidth="1" style="16" min="14" max="14"/>
+    <col width="9.138888888888889" customWidth="1" style="16" min="15" max="16384"/>
+    <col width="33.4907407407407" customWidth="1" min="16" max="16"/>
+    <col width="9.138888888888889" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2867,27 +2868,32 @@
           <t>Code Python thực tế (mapper.py)</t>
         </is>
       </c>
-      <c r="J1" s="18" t="inlineStr">
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t>Code giả dễ hiểu</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>Confirm mapping by dev</t>
         </is>
       </c>
-      <c r="K1" s="19" t="inlineStr">
+      <c r="L1" s="19" t="inlineStr">
         <is>
           <t>AI related?</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>Confirm 'AI related' by dev</t>
         </is>
       </c>
-      <c r="M1" s="22" t="inlineStr">
+      <c r="N1" s="22" t="inlineStr">
         <is>
           <t>Mô tả liên quan trong PRD</t>
         </is>
       </c>
-      <c r="N1" s="22" t="inlineStr">
+      <c r="O1" s="22" t="inlineStr">
         <is>
           <t>QC need cf?</t>
         </is>
@@ -2940,22 +2946,28 @@
           <t>output["request_id"] = input_data.get("request_id", str(uuid.uuid4()))</t>
         </is>
       </c>
-      <c r="J2" s="25" t="inlineStr">
+      <c r="J2" s="24" t="inlineStr">
+        <is>
+          <t>output.request_id ← input.request_id
+NẾU input không có request_id → tạo UUID mới</t>
+        </is>
+      </c>
+      <c r="K2" s="25" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr">
+      <c r="L2" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L2" s="25" t="inlineStr">
+      <c r="M2" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M2" s="25" t="inlineStr">
+      <c r="N2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nguồn: PRD Patient Summary.docx — Phần II, Phụ lục D — kiểm tra tích hợp
 Kiểm tra AI Service tiếp nhận request, bảo toàn requestId và trả response/errors đúng contract
@@ -3011,22 +3023,27 @@
 visit_count = len(visits)</t>
         </is>
       </c>
-      <c r="J3" s="26" t="inlineStr">
+      <c r="J3" s="24" t="inlineStr">
+        <is>
+          <t>visitCount ← số phần tử trong visits[]</t>
+        </is>
+      </c>
+      <c r="K3" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K3" s="23" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L3" s="25" t="inlineStr">
+      <c r="M3" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M3" s="26" t="inlineStr">
+      <c r="N3" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 5 — template response
 Payload dưới đây là template cấu trúc response đã chốt. Giá trị chỉ để minh họa và không phải expected output của input tại mục 2.5. Không bổ sung field ngoài contract. "visitCount": 3,
@@ -3086,22 +3103,28 @@
 latest_visit_date = latest_visit.get("visit_date", "")</t>
         </is>
       </c>
-      <c r="J4" s="26" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
+        <is>
+          <t>SẮP XẾP visits theo visit_date mới → cũ
+latestVisitDate ← visit_date của lượt đầu tiên</t>
+        </is>
+      </c>
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="N4" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Lượt khám có visitDate gần nhất trong toàn bộ visits[] luôn được đưa vào latestBySpecialty.
@@ -3162,22 +3185,28 @@
         specialties.append(specialty)</t>
         </is>
       </c>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="J5" s="24" t="inlineStr">
+        <is>
+          <t>specialties ← danh sách rỗng
+CHO MỖI visit → thêm specialty nếu khác rỗng và chưa có</t>
+        </is>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr">
+      <c r="N5" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.2
 specialty
@@ -3234,27 +3263,24 @@
       </c>
       <c r="G6" s="24" t="inlineStr"/>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="69" t="inlineStr">
-        <is>
-          <t>one_liner = _ai_str_if(_get_one_liner_ai_inputs(visits))</t>
-        </is>
-      </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="I6" s="69" t="n"/>
+      <c r="J6" s="24" t="n"/>
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K6" s="27" t="inlineStr">
+      <c r="L6" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L6" s="26" t="inlineStr">
+      <c r="M6" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M6" s="28" t="inlineStr">
+      <c r="N6" s="28" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.1
 4.1. One-liner
@@ -3305,27 +3331,24 @@
       </c>
       <c r="G7" s="24" t="inlineStr"/>
       <c r="H7" s="24" t="n"/>
-      <c r="I7" s="69" t="inlineStr">
-        <is>
-          <t>alerts = _ai_list_if(_get_allergy_ai_inputs(visits))</t>
-        </is>
-      </c>
-      <c r="J7" s="26" t="inlineStr">
+      <c r="I7" s="69" t="n"/>
+      <c r="J7" s="24" t="n"/>
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t>out = AI_summarize(in)</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L7" s="26" t="inlineStr">
+      <c r="M7" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr">
+      <c r="N7" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.2
 4.2. Cảnh báo dị ứng
@@ -3389,22 +3412,27 @@
 # mapper.py không dựng riêng alerts[].type; toàn bộ alerts là placeholder AI.</t>
         </is>
       </c>
-      <c r="J8" s="29" t="inlineStr">
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t>Code chưa tạo riêng alerts[].type; field này nằm trong placeholder AI của alerts.</t>
+        </is>
+      </c>
+      <c r="K8" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L8" s="25" t="inlineStr">
+      <c r="M8" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M8" s="29" t="inlineStr">
+      <c r="N8" s="29" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 5 — template response
 Payload dưới đây là template cấu trúc response đã chốt. Giá trị chỉ để minh họa và không phải expected output của input tại mục 2.5. Không bổ sung field ngoài contract. "type": "warning",
@@ -3443,28 +3471,24 @@
       </c>
       <c r="G9" s="32" t="inlineStr"/>
       <c r="H9" s="32" t="n"/>
-      <c r="I9" s="70" t="inlineStr">
-        <is>
-          <t>alerts = _ai_list_if(_get_allergy_ai_inputs(visits))
-# mapper.py không dựng riêng alerts[].title; toàn bộ alerts là placeholder AI.</t>
-        </is>
-      </c>
-      <c r="J9" s="33" t="inlineStr">
+      <c r="I9" s="70" t="n"/>
+      <c r="J9" s="32" t="n"/>
+      <c r="K9" s="33" t="inlineStr">
         <is>
           <t>out = AI_summarize(in)</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L9" s="33" t="inlineStr">
+      <c r="M9" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.9 — Cảnh báo dị ứng
 Tên tác nhân; biểu hiện; ngày ghi nhận; *khoa ghi nhận; ghi chú phạm vi tổng hợp; *cờ mâu thuẫn nếu các nguồn ghi khác nhau
@@ -3473,7 +3497,7 @@
           "title": "Dị ứng Amoxicillin",</t>
         </is>
       </c>
-      <c r="N9" s="34" t="n"/>
+      <c r="O9" s="34" t="n"/>
     </row>
     <row r="10" ht="244.5" customFormat="1" customHeight="1" s="14">
       <c r="A10" s="23" t="n">
@@ -3506,28 +3530,24 @@
       </c>
       <c r="G10" s="32" t="inlineStr"/>
       <c r="H10" s="32" t="n"/>
-      <c r="I10" s="70" t="inlineStr">
-        <is>
-          <t>alerts = _ai_list_if(_get_allergy_ai_inputs(visits))
-# mapper.py không dựng riêng alerts[].description; toàn bộ alerts là placeholder AI.</t>
-        </is>
-      </c>
-      <c r="J10" s="33" t="inlineStr">
+      <c r="I10" s="70" t="n"/>
+      <c r="J10" s="32" t="n"/>
+      <c r="K10" s="33" t="inlineStr">
         <is>
           <t>out = AI_summarize(in)</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L10" s="33" t="inlineStr">
+      <c r="M10" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.2
 Nguồn gồm history.allergy và prescriptions[].allergyOnPrescription trong phạm vi payload; scopeNote phải nêu rõ phạm vi tổng hợp.
@@ -3538,7 +3558,7 @@
           "description": "Nổi mẩn đỏ, ghi nhận ngày 07/02/2026.",</t>
         </is>
       </c>
-      <c r="N10" s="34" t="n"/>
+      <c r="O10" s="34" t="n"/>
     </row>
     <row r="11" ht="60.75" customFormat="1" customHeight="1" s="14">
       <c r="A11" s="23" t="n">
@@ -3571,34 +3591,30 @@
       </c>
       <c r="G11" s="32" t="inlineStr"/>
       <c r="H11" s="32" t="n"/>
-      <c r="I11" s="70" t="inlineStr">
-        <is>
-          <t>alerts = _ai_list_if(_get_allergy_ai_inputs(visits))
-# mapper.py không dựng riêng alerts[].identifiedDate; toàn bộ alerts là placeholder AI.</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="inlineStr">
+      <c r="I11" s="70" t="n"/>
+      <c r="J11" s="32" t="n"/>
+      <c r="K11" s="23" t="inlineStr">
         <is>
           <t>out = AI_summarize(in)</t>
         </is>
       </c>
-      <c r="K11" s="23" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L11" s="23" t="inlineStr">
+      <c r="M11" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M11" s="23" t="inlineStr">
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.2
 identifiedDate chỉ điền khi nguồn có ngày ghi nhận; không dùng visitDate thay cho ngày phát hiện nếu nguồn không xác nhận.</t>
         </is>
       </c>
-      <c r="N11" s="34" t="n"/>
+      <c r="O11" s="34" t="n"/>
     </row>
     <row r="12" ht="106.5" customHeight="1">
       <c r="A12" s="23" t="n">
@@ -3632,28 +3648,24 @@
       </c>
       <c r="G12" s="32" t="inlineStr"/>
       <c r="H12" s="32" t="n"/>
-      <c r="I12" s="70" t="inlineStr">
-        <is>
-          <t>alerts = _ai_list_if(_get_allergy_ai_inputs(visits))
-# mapper.py không dựng riêng alerts[].conflict; toàn bộ alerts là placeholder AI.</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="inlineStr">
+      <c r="I12" s="70" t="n"/>
+      <c r="J12" s="32" t="n"/>
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>out = AI_summarize(in)</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L12" s="23" t="inlineStr">
+      <c r="M12" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="N12" s="23" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.2
 Nếu các lượt hoặc hai nguồn ghi khác nhau, alerts trả cả hai nội dung, đặt conflict=true và không tự chọn nguồn đúng.
@@ -3661,7 +3673,7 @@
           "conflict": false,</t>
         </is>
       </c>
-      <c r="N12" s="35" t="n"/>
+      <c r="O12" s="35" t="n"/>
     </row>
     <row r="13" ht="137.25" customHeight="1">
       <c r="A13" s="23" t="n">
@@ -3690,28 +3702,24 @@
       </c>
       <c r="G13" s="24" t="inlineStr"/>
       <c r="H13" s="24" t="n"/>
-      <c r="I13" s="69" t="inlineStr">
-        <is>
-          <t>alerts = _ai_list_if(_get_allergy_ai_inputs(visits))
-# mapper.py không dựng riêng alerts[].scopeNote; toàn bộ alerts là placeholder AI.</t>
-        </is>
-      </c>
-      <c r="J13" s="30" t="inlineStr">
+      <c r="I13" s="69" t="n"/>
+      <c r="J13" s="24" t="n"/>
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t>out = AI_summarize(in)</t>
         </is>
       </c>
-      <c r="K13" s="27" t="inlineStr">
+      <c r="L13" s="27" t="inlineStr">
         <is>
           <t>Không chắc</t>
         </is>
       </c>
-      <c r="L13" s="29" t="inlineStr">
+      <c r="M13" s="29" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr">
+      <c r="N13" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.2
 Nguồn gồm history.allergy và prescriptions[].allergyOnPrescription trong phạm vi payload; scopeNote phải nêu rõ phạm vi tổng hợp.
@@ -3771,22 +3779,27 @@
 section_4 = {"order": 4, ...}</t>
         </is>
       </c>
-      <c r="J14" s="23" t="inlineStr">
+      <c r="J14" s="32" t="inlineStr">
+        <is>
+          <t>GÁN cố định order của 4 section lần lượt là 1, 2, 3, 4.</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K14" s="36" t="inlineStr">
+      <c r="L14" s="36" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L14" s="23" t="inlineStr">
+      <c r="M14" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M14" s="26" t="inlineStr">
+      <c r="N14" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 5 — template response
 Payload dưới đây là template cấu trúc response đã chốt. Giá trị chỉ để minh họa và không phải expected output của input tại mục 2.5. Không bổ sung field ngoài contract.
@@ -3855,22 +3868,29 @@
 section_4 = {"title": "Việc cần theo dõi tiếp", ...}</t>
         </is>
       </c>
-      <c r="J15" s="23" t="inlineStr">
+      <c r="J15" s="32" t="inlineStr">
+        <is>
+          <t>GÁN cố định title theo order:
+1 Tiền sử nền; 2 Thuốc đang sử dụng;
+3 Tình trạng bệnh nhân; 4 Việc cần theo dõi tiếp.</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K15" s="36" t="inlineStr">
+      <c r="L15" s="36" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L15" s="23" t="inlineStr">
+      <c r="M15" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M15" s="26" t="inlineStr">
+      <c r="N15" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 5 — template response
 Payload dưới đây là template cấu trúc response đã chốt. Giá trị chỉ để minh họa và không phải expected output của input tại mục 2.5. Không bổ sung field ngoài contract.
@@ -3920,27 +3940,24 @@
       </c>
       <c r="G16" s="24" t="inlineStr"/>
       <c r="H16" s="24" t="n"/>
-      <c r="I16" s="69" t="inlineStr">
-        <is>
-          <t>items = _ai_list_if(_get_background_history_ai_inputs(visits))</t>
-        </is>
-      </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="I16" s="69" t="n"/>
+      <c r="J16" s="24" t="n"/>
+      <c r="K16" s="27" t="inlineStr">
         <is>
           <t>out = AI_summarize(in)</t>
         </is>
       </c>
-      <c r="K16" s="37" t="inlineStr">
+      <c r="L16" s="37" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L16" s="23" t="inlineStr">
+      <c r="M16" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M16" s="26" t="inlineStr">
+      <c r="N16" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.3
 4.3. Tiền sử nền
@@ -3991,28 +4008,24 @@
       </c>
       <c r="G17" s="24" t="inlineStr"/>
       <c r="H17" s="24" t="n"/>
-      <c r="I17" s="69" t="inlineStr">
-        <is>
-          <t>items = _ai_list_if(_get_background_history_ai_inputs(visits))
-# mapper.py không dựng riêng items[].since; toàn bộ items là placeholder AI.</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="I17" s="69" t="n"/>
+      <c r="J17" s="24" t="n"/>
+      <c r="K17" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K17" s="23" t="inlineStr">
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="M17" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M17" s="26" t="inlineStr">
+      <c r="N17" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.3
 items[].since chỉ điền mốc tháng/năm khi nguồn ghi rõ; không có mốc thì trả chuỗi rỗng.
@@ -4021,7 +4034,7 @@
               "since": "01/2026"</t>
         </is>
       </c>
-      <c r="N17" s="38" t="inlineStr">
+      <c r="O17" s="38" t="inlineStr">
         <is>
           <t>Lấy thời gian sớm nhất; nếu không phân biệt được mm/dd/ và dd/mm, thì ưu tiên map với dd/mm</t>
         </is>
@@ -4058,30 +4071,24 @@
       </c>
       <c r="G18" s="24" t="inlineStr"/>
       <c r="H18" s="24" t="n"/>
-      <c r="I18" s="69" t="inlineStr">
-        <is>
-          <t>family_history = _ai_list_if([
-    (visit.get("history") or {}).get("family_history")
-    for visit in visits
-])</t>
-        </is>
-      </c>
-      <c r="J18" s="26" t="inlineStr">
+      <c r="I18" s="69" t="n"/>
+      <c r="J18" s="24" t="n"/>
+      <c r="K18" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K18" s="23" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L18" s="26" t="inlineStr">
+      <c r="M18" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M18" s="26" t="inlineStr">
+      <c r="N18" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.3
 Tổng hợp từ toàn bộ visits[] trong phạm vi, không chỉ lượt gần nhất; khử trùng lặp nhưng không làm mất khác biệt có ý nghĩa.
@@ -4123,29 +4130,24 @@
       </c>
       <c r="G19" s="24" t="inlineStr"/>
       <c r="H19" s="24" t="n"/>
-      <c r="I19" s="69" t="inlineStr">
-        <is>
-          <t>obstetric_history = _ai_str_if(
-    _get_obstetric_history_ai_inputs(visits, "obstetric_history")
-)</t>
-        </is>
-      </c>
-      <c r="J19" s="26" t="inlineStr">
+      <c r="I19" s="69" t="n"/>
+      <c r="J19" s="24" t="n"/>
+      <c r="K19" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K19" s="23" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L19" s="26" t="inlineStr">
+      <c r="M19" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M19" s="26" t="inlineStr">
+      <c r="N19" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.3
 Tổng hợp từ toàn bộ visits[] trong phạm vi, không chỉ lượt gần nhất; khử trùng lặp nhưng không làm mất khác biệt có ý nghĩa.
@@ -4186,29 +4188,24 @@
       </c>
       <c r="G20" s="24" t="inlineStr"/>
       <c r="H20" s="24" t="n"/>
-      <c r="I20" s="69" t="inlineStr">
-        <is>
-          <t>menstrual_history = _ai_str_if(
-    _get_obstetric_history_ai_inputs(visits, "menstrual_history")
-)</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="inlineStr">
+      <c r="I20" s="69" t="n"/>
+      <c r="J20" s="24" t="n"/>
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K20" s="23" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L20" s="26" t="inlineStr">
+      <c r="M20" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M20" s="26" t="inlineStr">
+      <c r="N20" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.3
 Tổng hợp từ toàn bộ visits[] trong phạm vi, không chỉ lượt gần nhất; khử trùng lặp nhưng không làm mất khác biệt có ý nghĩa.
@@ -4270,22 +4267,28 @@
 "name": name_val</t>
         </is>
       </c>
-      <c r="J21" s="26" t="inlineStr">
+      <c r="J21" s="24" t="inlineStr">
+        <is>
+          <t>Với thuốc thuộc đơn mới nhất hoặc còn hạn:
+name ← item.name</t>
+        </is>
+      </c>
+      <c r="K21" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K21" s="27" t="inlineStr">
+      <c r="L21" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="M21" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M21" s="26" t="inlineStr">
+      <c r="N21" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.4
 Danh sách thuốc: name (tên và hàm lượng), dosageInstruction (liều và cách dùng, nguyên văn), route, quantity, duration, note
@@ -4352,22 +4355,27 @@
 "dosage": dosage_extracted</t>
         </is>
       </c>
-      <c r="J22" s="26" t="inlineStr">
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>dosage ← tìm cụm số + đơn vị (mg, ml, g, mcg, IU...) trong item.name</t>
+        </is>
+      </c>
+      <c r="K22" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K22" s="23" t="inlineStr">
+      <c r="L22" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L22" s="26" t="inlineStr">
+      <c r="M22" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M22" s="26" t="inlineStr">
+      <c r="N22" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.4
 Field đầu ra: name, dosage, frequency, prescribedDate, prescriptionCode, specialty và durationEndDate. dosage và frequency chỉ tách khi dosageInstruction đủ rõ; không tách được thì dùng chuỗi rỗng.
@@ -4427,22 +4435,27 @@
 "frequency": frequency_extracted</t>
         </is>
       </c>
-      <c r="J23" s="26" t="inlineStr">
+      <c r="J23" s="24" t="inlineStr">
+        <is>
+          <t>frequency ← giữ nguyên toàn bộ item.dosage_instruction; không tách nhỏ.</t>
+        </is>
+      </c>
+      <c r="K23" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K23" s="23" t="inlineStr">
+      <c r="L23" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L23" s="26" t="inlineStr">
+      <c r="M23" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M23" s="26" t="inlineStr">
+      <c r="N23" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.4
 Field đầu ra: name, dosage, frequency, prescribedDate, prescriptionCode, specialty và durationEndDate. dosage và frequency chỉ tách khi dosageInstruction đủ rõ; không tách được thì dùng chuỗi rỗng.
@@ -4499,22 +4512,27 @@
           <t>"quantity": item.get("quantity", "")</t>
         </is>
       </c>
-      <c r="J24" s="26" t="inlineStr">
+      <c r="J24" s="24" t="inlineStr">
+        <is>
+          <t>quantity ← item.quantity</t>
+        </is>
+      </c>
+      <c r="K24" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr">
+      <c r="L24" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L24" s="26" t="inlineStr">
+      <c r="M24" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M24" s="26" t="inlineStr">
+      <c r="N24" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.4 — input
 Danh sách thuốc: name (tên và hàm lượng), dosageInstruction (liều và cách dùng, nguyên văn), route, quantity, duration, note
@@ -4577,22 +4595,27 @@
 "prescribedDate": prescribed_date</t>
         </is>
       </c>
-      <c r="J25" s="26" t="inlineStr">
+      <c r="J25" s="24" t="inlineStr">
+        <is>
+          <t>prescribedDate ← prescription.prescribed_date</t>
+        </is>
+      </c>
+      <c r="K25" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K25" s="23" t="inlineStr">
+      <c r="L25" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L25" s="26" t="inlineStr">
+      <c r="M25" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M25" s="26" t="inlineStr">
+      <c r="N25" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.4
 prescribedDate
@@ -4652,22 +4675,27 @@
           <t>"prescriptionCode": p.get("prescription_code", "")</t>
         </is>
       </c>
-      <c r="J26" s="26" t="inlineStr">
+      <c r="J26" s="24" t="inlineStr">
+        <is>
+          <t>prescriptionCode ← prescription.prescription_code</t>
+        </is>
+      </c>
+      <c r="K26" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K26" s="23" t="inlineStr">
+      <c r="L26" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L26" s="26" t="inlineStr">
+      <c r="M26" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M26" s="26" t="inlineStr">
+      <c r="N26" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.4
 prescriptionCode
@@ -4727,22 +4755,27 @@
           <t>"specialty": p.get("specialty", "")</t>
         </is>
       </c>
-      <c r="J27" s="26" t="inlineStr">
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>specialty ← prescription.specialty</t>
+        </is>
+      </c>
+      <c r="K27" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K27" s="23" t="inlineStr">
+      <c r="L27" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L27" s="26" t="inlineStr">
+      <c r="M27" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M27" s="26" t="inlineStr">
+      <c r="N27" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.4
 specialty: lấy từ prescriptions[].specialty, không thay bằng specialty của lượt khám.
@@ -4803,22 +4836,27 @@
 "durationEndDate": duration_end_date</t>
         </is>
       </c>
-      <c r="J28" s="26" t="inlineStr">
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>durationEndDate ← item.stop_date</t>
+        </is>
+      </c>
+      <c r="K28" s="26" t="inlineStr">
         <is>
           <t>data.summary.sections[order=2].byPrescription[].durationEndDate = visits[].prescriptions[].items[].stop_date</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr">
+      <c r="L28" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L28" s="26" t="inlineStr">
+      <c r="M28" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M28" s="26" t="inlineStr">
+      <c r="N28" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.4
 durationEndDate: tính từ prescribedDate và duration khi duration có số ngày rõ ràng; không đủ dữ liệu thì trả chuỗi rỗng, không ước lượng.
@@ -4875,22 +4913,29 @@
           <t>"name": m.get("name", "")</t>
         </is>
       </c>
-      <c r="J29" s="26" t="inlineStr">
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>CHO MỖI thuốc trong current_medications của lượt mới nhất
+→ name ← medication.name
+Lưu ý: code hiện không kiểm tra medication_status.</t>
+        </is>
+      </c>
+      <c r="K29" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K29" s="23" t="inlineStr">
+      <c r="L29" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L29" s="26" t="inlineStr">
+      <c r="M29" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M29" s="26" t="inlineStr">
+      <c r="N29" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.4
 selfReported: lấy từ history.currentMedications[]; trả name, dosage, route và askedDate. askedDate là visitDate của phiếu ghi nhận. lastDoseDate không có field tương ứng trong response và không được tự gộp vào field khác.
@@ -4950,22 +4995,27 @@
           <t>"dosage": m.get("dosage", "")</t>
         </is>
       </c>
-      <c r="J30" s="26" t="inlineStr">
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>dosage ← medication.dosage của current_medications ở lượt mới nhất.</t>
+        </is>
+      </c>
+      <c r="K30" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K30" s="23" t="inlineStr">
+      <c r="L30" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L30" s="26" t="inlineStr">
+      <c r="M30" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M30" s="26" t="inlineStr">
+      <c r="N30" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.4
 selfReported: lấy từ history.currentMedications[]; trả name, dosage, route và askedDate. askedDate là visitDate của phiếu ghi nhận. lastDoseDate không có field tương ứng trong response và không được tự gộp vào field khác.
@@ -5025,22 +5075,27 @@
           <t>"route": m.get("route", "")</t>
         </is>
       </c>
-      <c r="J31" s="26" t="inlineStr">
+      <c r="J31" s="24" t="inlineStr">
+        <is>
+          <t>route ← medication.route của current_medications ở lượt mới nhất.</t>
+        </is>
+      </c>
+      <c r="K31" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K31" s="23" t="inlineStr">
+      <c r="L31" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L31" s="26" t="inlineStr">
+      <c r="M31" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M31" s="26" t="inlineStr">
+      <c r="N31" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.4
 selfReported: lấy từ history.currentMedications[]; trả name, dosage, route và askedDate. askedDate là visitDate của phiếu ghi nhận. lastDoseDate không có field tương ứng trong response và không được tự gộp vào field khác.
@@ -5100,22 +5155,27 @@
           <t>"askedDate": latest_visit.get("visit_date", "")</t>
         </is>
       </c>
-      <c r="J32" s="26" t="inlineStr">
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>askedDate ← visit_date của lượt khám mới nhất.</t>
+        </is>
+      </c>
+      <c r="K32" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr">
+      <c r="L32" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L32" s="26" t="inlineStr">
+      <c r="M32" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M32" s="26" t="inlineStr">
+      <c r="N32" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.4
 selfReported: lấy từ history.currentMedications[]; trả name, dosage, route và askedDate. askedDate là visitDate của phiếu ghi nhận. lastDoseDate không có field tương ứng trong response và không được tự gộp vào field khác.</t>
@@ -5179,22 +5239,29 @@
 )</t>
         </is>
       </c>
-      <c r="J33" s="26" t="inlineStr">
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>selectedVisits ← mọi lượt có ngày khám mới nhất toàn cục
++ các lượt cũ có ít nhất một item.stop_date còn hạn
+SAU ĐÓ bỏ trùng và sắp xếp ngày giảm dần</t>
+        </is>
+      </c>
+      <c r="K33" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K33" s="27" t="inlineStr">
+      <c r="L33" s="27" t="inlineStr">
         <is>
           <t>Không chắc</t>
         </is>
       </c>
-      <c r="L33" s="26" t="inlineStr">
+      <c r="M33" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M33" s="26" t="inlineStr">
+      <c r="N33" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Lượt khám có visitDate gần nhất trong toàn bộ visits[] luôn được đưa vào latestBySpecialty.
@@ -5205,7 +5272,7 @@
 Mọi lượt khám hợp lệ trong phạm vi, kể cả lượt không được chọn vào latestBySpecialty, vẫn phải xuất hiện trong timeline.</t>
         </is>
       </c>
-      <c r="N33" s="38" t="inlineStr">
+      <c r="O33" s="38" t="inlineStr">
         <is>
           <t>visits[].prescriptions[].items[].duration (hiện không dùng): tức không impact tới latestBySpecialty trong response;</t>
         </is>
@@ -5257,22 +5324,27 @@
           <t>"visitDate": v_sel.get("visit_date", "")</t>
         </is>
       </c>
-      <c r="J34" s="26" t="inlineStr">
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>CHO MỖI selectedVisit → visitDate ← selectedVisit.visit_date</t>
+        </is>
+      </c>
+      <c r="K34" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K34" s="23" t="inlineStr">
+      <c r="L34" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L34" s="26" t="inlineStr">
+      <c r="M34" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M34" s="26" t="inlineStr">
+      <c r="N34" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Mỗi khối chỉ dùng dữ liệu của chính lượt được chọn; không lấy dữ liệu của lượt khác để lấp field trống.
@@ -5327,22 +5399,27 @@
           <t>"specialty": v_sel.get("specialty", "")</t>
         </is>
       </c>
-      <c r="J35" s="26" t="inlineStr">
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>CHO MỖI selectedVisit → specialty ← selectedVisit.specialty</t>
+        </is>
+      </c>
+      <c r="K35" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K35" s="23" t="inlineStr">
+      <c r="L35" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L35" s="26" t="inlineStr">
+      <c r="M35" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M35" s="26" t="inlineStr">
+      <c r="N35" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Mỗi khối chỉ dùng dữ liệu của chính lượt được chọn; không lấy dữ liệu của lượt khác để lấp field trống.
@@ -5397,22 +5474,27 @@
           <t>"pulse": _normalize_number(vitals.get("pulse"))</t>
         </is>
       </c>
-      <c r="J36" s="26" t="inlineStr">
+      <c r="J36" s="24" t="inlineStr">
+        <is>
+          <t>pulse ← đổi vitals.pulse thành số; lỗi/rỗng → 0</t>
+        </is>
+      </c>
+      <c r="K36" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K36" s="23" t="inlineStr">
+      <c r="L36" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L36" s="26" t="inlineStr">
+      <c r="M36" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M36" s="26" t="inlineStr">
+      <c r="N36" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Mỗi khối chỉ dùng dữ liệu của chính lượt được chọn; không lấy dữ liệu của lượt khác để lấp field trống.
@@ -5475,22 +5557,27 @@
           <t>"bloodPressure": str(vitals.get("blood_pressure", ""))</t>
         </is>
       </c>
-      <c r="J37" s="26" t="inlineStr">
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>bloodPressure ← đổi vitals.blood_pressure thành chuỗi.</t>
+        </is>
+      </c>
+      <c r="K37" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K37" s="23" t="inlineStr">
+      <c r="L37" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L37" s="26" t="inlineStr">
+      <c r="M37" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M37" s="26" t="inlineStr">
+      <c r="N37" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Mỗi khối chỉ dùng dữ liệu của chính lượt được chọn; không lấy dữ liệu của lượt khác để lấp field trống.
@@ -5552,22 +5639,27 @@
           <t>"spo2": _normalize_number(vitals.get("spo2"))</t>
         </is>
       </c>
-      <c r="J38" s="26" t="inlineStr">
+      <c r="J38" s="24" t="inlineStr">
+        <is>
+          <t>spo2 ← đổi vitals.spo2 thành số; lỗi/rỗng → 0</t>
+        </is>
+      </c>
+      <c r="K38" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K38" s="23" t="inlineStr">
+      <c r="L38" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L38" s="26" t="inlineStr">
+      <c r="M38" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M38" s="26" t="inlineStr">
+      <c r="N38" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Mỗi khối chỉ dùng dữ liệu của chính lượt được chọn; không lấy dữ liệu của lượt khác để lấp field trống.
@@ -5629,22 +5721,27 @@
           <t>"respiratoryRate": _normalize_number(vitals.get("respiratory_rate"))</t>
         </is>
       </c>
-      <c r="J39" s="26" t="inlineStr">
+      <c r="J39" s="24" t="inlineStr">
+        <is>
+          <t>respiratoryRate ← đổi vitals.respiratory_rate thành số; lỗi/rỗng → 0</t>
+        </is>
+      </c>
+      <c r="K39" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K39" s="23" t="inlineStr">
+      <c r="L39" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L39" s="26" t="inlineStr">
+      <c r="M39" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M39" s="26" t="inlineStr">
+      <c r="N39" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Mỗi khối chỉ dùng dữ liệu của chính lượt được chọn; không lấy dữ liệu của lượt khác để lấp field trống.
@@ -5706,22 +5803,27 @@
           <t>"weight": _normalize_number(vitals.get("weight_kg"))</t>
         </is>
       </c>
-      <c r="J40" s="26" t="inlineStr">
+      <c r="J40" s="24" t="inlineStr">
+        <is>
+          <t>weight ← đổi vitals.weight_kg thành số; lỗi/rỗng → 0</t>
+        </is>
+      </c>
+      <c r="K40" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K40" s="23" t="inlineStr">
+      <c r="L40" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L40" s="26" t="inlineStr">
+      <c r="M40" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M40" s="26" t="inlineStr">
+      <c r="N40" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Mỗi khối chỉ dùng dữ liệu của chính lượt được chọn; không lấy dữ liệu của lượt khác để lấp field trống.
@@ -5783,22 +5885,27 @@
           <t>"height": _normalize_number(vitals.get("height_cm"))</t>
         </is>
       </c>
-      <c r="J41" s="26" t="inlineStr">
+      <c r="J41" s="24" t="inlineStr">
+        <is>
+          <t>height ← đổi vitals.height_cm thành số; lỗi/rỗng → 0</t>
+        </is>
+      </c>
+      <c r="K41" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K41" s="23" t="inlineStr">
+      <c r="L41" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L41" s="26" t="inlineStr">
+      <c r="M41" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M41" s="26" t="inlineStr">
+      <c r="N41" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Mỗi khối chỉ dùng dữ liệu của chính lượt được chọn; không lấy dữ liệu của lượt khác để lấp field trống.
@@ -5860,22 +5967,27 @@
           <t>"temperature": _normalize_number(vitals.get("temperature"))</t>
         </is>
       </c>
-      <c r="J42" s="26" t="inlineStr">
+      <c r="J42" s="24" t="inlineStr">
+        <is>
+          <t>temperature ← đổi vitals.temperature thành số; lỗi/rỗng → 0</t>
+        </is>
+      </c>
+      <c r="K42" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K42" s="23" t="inlineStr">
+      <c r="L42" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L42" s="26" t="inlineStr">
+      <c r="M42" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M42" s="26" t="inlineStr">
+      <c r="N42" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 temperature và bmi: không có field riêng trong vitalSigns của response. Không tạo field mới; nếu cần giữ nội dung nguồn thì đưa vào timeline.details.clinical của đúng lượt.
@@ -5932,22 +6044,27 @@
           <t>"bmi": _normalize_number(vitals.get("bmi"))</t>
         </is>
       </c>
-      <c r="J43" s="26" t="inlineStr">
+      <c r="J43" s="24" t="inlineStr">
+        <is>
+          <t>bmi ← đổi vitals.bmi thành số; lỗi/rỗng → 0</t>
+        </is>
+      </c>
+      <c r="K43" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K43" s="23" t="inlineStr">
+      <c r="L43" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L43" s="26" t="inlineStr">
+      <c r="M43" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M43" s="26" t="inlineStr">
+      <c r="N43" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 temperature và bmi: không có field riêng trong vitalSigns của response. Không tạo field mới; nếu cần giữ nội dung nguồn thì đưa vào timeline.details.clinical của đúng lượt.
@@ -5988,27 +6105,24 @@
       </c>
       <c r="G44" s="24" t="inlineStr"/>
       <c r="H44" s="24" t="n"/>
-      <c r="I44" s="69" t="inlineStr">
-        <is>
-          <t>"clinicalFindings": _ai_str_if(_get_examination_ai_inputs(v_sel))</t>
-        </is>
-      </c>
-      <c r="J44" s="26" t="inlineStr">
+      <c r="I44" s="69" t="n"/>
+      <c r="J44" s="24" t="n"/>
+      <c r="K44" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K44" s="27" t="inlineStr">
+      <c r="L44" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L44" s="23" t="inlineStr">
+      <c r="M44" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M44" s="26" t="inlineStr">
+      <c r="N44" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.1
 Mỗi khối chỉ dùng dữ liệu của chính lượt được chọn; không lấy dữ liệu của lượt khác để lấp field trống.
@@ -6051,27 +6165,24 @@
       </c>
       <c r="G45" s="24" t="inlineStr"/>
       <c r="H45" s="24" t="n"/>
-      <c r="I45" s="69" t="inlineStr">
-        <is>
-          <t>"obstetrics": _build_obstetrics(v_sel)</t>
-        </is>
-      </c>
-      <c r="J45" s="26" t="inlineStr">
+      <c r="I45" s="69" t="n"/>
+      <c r="J45" s="24" t="n"/>
+      <c r="K45" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K45" s="27" t="inlineStr">
+      <c r="L45" s="27" t="inlineStr">
         <is>
           <t>Không chắc</t>
         </is>
       </c>
-      <c r="L45" s="26" t="inlineStr">
+      <c r="M45" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M45" s="26" t="inlineStr">
+      <c r="N45" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 specialtyFindings: obstetrics chỉ lấy nội dung khám chuyên khoa Sản có trong examination; pediatrics map bốn trường đánh giá Nhi. Nhóm không áp dụng dùng null hoặc object rỗng đúng template.
@@ -6136,22 +6247,29 @@
 "nutrition": exam.get("nutrition_assessment") or exam.get("nutrition assessment") or ""</t>
         </is>
       </c>
-      <c r="J46" s="26" t="inlineStr">
+      <c r="J46" s="24" t="inlineStr">
+        <is>
+          <t>nutrition ← examination.nutrition_assessment
+NẾU không có → thử key 'nutrition assessment'; cuối cùng → ''
+Lưu ý: code không kiểm tra specialty Nhi.</t>
+        </is>
+      </c>
+      <c r="K46" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K46" s="23" t="inlineStr">
+      <c r="L46" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L46" s="26" t="inlineStr">
+      <c r="M46" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M46" s="26" t="inlineStr">
+      <c r="N46" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 specialtyFindings: obstetrics chỉ lấy nội dung khám chuyên khoa Sản có trong examination; pediatrics map bốn trường đánh giá Nhi. Nhóm không áp dụng dùng null hoặc object rỗng đúng template.
@@ -6213,22 +6331,29 @@
 "vaccination": exam.get("vaccination_assessment") or exam.get("vaccination assessment") or ""</t>
         </is>
       </c>
-      <c r="J47" s="26" t="inlineStr">
+      <c r="J47" s="24" t="inlineStr">
+        <is>
+          <t>vaccination ← examination.vaccination_assessment
+NẾU không có → thử key 'vaccination assessment'; cuối cùng → ''
+Lưu ý: code không kiểm tra specialty Nhi.</t>
+        </is>
+      </c>
+      <c r="K47" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K47" s="23" t="inlineStr">
+      <c r="L47" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L47" s="26" t="inlineStr">
+      <c r="M47" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M47" s="26" t="inlineStr">
+      <c r="N47" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 specialtyFindings: obstetrics chỉ lấy nội dung khám chuyên khoa Sản có trong examination; pediatrics map bốn trường đánh giá Nhi. Nhóm không áp dụng dùng null hoặc object rỗng đúng template.
@@ -6290,22 +6415,29 @@
 "motorDevelopment": exam.get("motor_development") or exam.get("motor development") or ""</t>
         </is>
       </c>
-      <c r="J48" s="26" t="inlineStr">
+      <c r="J48" s="24" t="inlineStr">
+        <is>
+          <t>motorDevelopment ← examination.motor_development
+NẾU không có → thử key 'motor development'; cuối cùng → ''
+Lưu ý: code không kiểm tra specialty Nhi.</t>
+        </is>
+      </c>
+      <c r="K48" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K48" s="23" t="inlineStr">
+      <c r="L48" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L48" s="26" t="inlineStr">
+      <c r="M48" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M48" s="26" t="inlineStr">
+      <c r="N48" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 specialtyFindings: obstetrics chỉ lấy nội dung khám chuyên khoa Sản có trong examination; pediatrics map bốn trường đánh giá Nhi. Nhóm không áp dụng dùng null hoặc object rỗng đúng template.
@@ -6367,22 +6499,29 @@
 "mentalDevelopment": exam.get("mental_development") or exam.get("mental development") or ""</t>
         </is>
       </c>
-      <c r="J49" s="26" t="inlineStr">
+      <c r="J49" s="24" t="inlineStr">
+        <is>
+          <t>mentalDevelopment ← examination.mental_development
+NẾU không có → thử key 'mental development'; cuối cùng → ''
+Lưu ý: code không kiểm tra specialty Nhi.</t>
+        </is>
+      </c>
+      <c r="K49" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K49" s="23" t="inlineStr">
+      <c r="L49" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L49" s="26" t="inlineStr">
+      <c r="M49" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M49" s="26" t="inlineStr">
+      <c r="N49" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 specialtyFindings: obstetrics chỉ lấy nội dung khám chuyên khoa Sản có trong examination; pediatrics map bốn trường đánh giá Nhi. Nhóm không áp dụng dùng null hoặc object rỗng đúng template.
@@ -6425,34 +6564,24 @@
       </c>
       <c r="G50" s="24" t="inlineStr"/>
       <c r="H50" s="24" t="n"/>
-      <c r="I50" s="69" t="inlineStr">
-        <is>
-          <t>"abnormalResults": (
-    AI_LIST
-    if _has_meaningful_abnormal_result(
-        (v_sel.get("labs") or {}).get("abnormal_result")
-    )
-    else []
-)
-# mapper.py không dựng riêng abnormalResults[].name.</t>
-        </is>
-      </c>
-      <c r="J50" s="26" t="inlineStr">
+      <c r="I50" s="69" t="n"/>
+      <c r="J50" s="24" t="n"/>
+      <c r="K50" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K50" s="27" t="inlineStr">
+      <c r="L50" s="27" t="inlineStr">
         <is>
           <t>Không chắc</t>
         </is>
       </c>
-      <c r="L50" s="26" t="inlineStr">
+      <c r="M50" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M50" s="26" t="inlineStr">
+      <c r="N50" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 abnormalResults: lấy từ labs.abnormalResult. abnormal phản ánh đúng đánh dấu của nguồn; AI không tự áp ngưỡng.
@@ -6495,34 +6624,24 @@
       </c>
       <c r="G51" s="24" t="inlineStr"/>
       <c r="H51" s="24" t="n"/>
-      <c r="I51" s="69" t="inlineStr">
-        <is>
-          <t>"abnormalResults": (
-    AI_LIST
-    if _has_meaningful_abnormal_result(
-        (v_sel.get("labs") or {}).get("abnormal_result")
-    )
-    else []
-)
-# mapper.py không dựng riêng abnormalResults[].result.</t>
-        </is>
-      </c>
-      <c r="J51" s="26" t="inlineStr">
+      <c r="I51" s="69" t="n"/>
+      <c r="J51" s="24" t="n"/>
+      <c r="K51" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K51" s="27" t="inlineStr">
+      <c r="L51" s="27" t="inlineStr">
         <is>
           <t>Không chắc</t>
         </is>
       </c>
-      <c r="L51" s="26" t="inlineStr">
+      <c r="M51" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M51" s="26" t="inlineStr">
+      <c r="N51" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 abnormalResults: lấy từ labs.abnormalResult. abnormal phản ánh đúng đánh dấu của nguồn; AI không tự áp ngưỡng.
@@ -6565,34 +6684,24 @@
       </c>
       <c r="G52" s="24" t="inlineStr"/>
       <c r="H52" s="24" t="n"/>
-      <c r="I52" s="69" t="inlineStr">
-        <is>
-          <t>"abnormalResults": (
-    AI_LIST
-    if _has_meaningful_abnormal_result(
-        (v_sel.get("labs") or {}).get("abnormal_result")
-    )
-    else []
-)
-# mapper.py không dựng riêng abnormalResults[].abnormal.</t>
-        </is>
-      </c>
-      <c r="J52" s="26" t="inlineStr">
+      <c r="I52" s="69" t="n"/>
+      <c r="J52" s="24" t="n"/>
+      <c r="K52" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K52" s="23" t="inlineStr">
+      <c r="L52" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L52" s="26" t="inlineStr">
+      <c r="M52" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M52" s="26" t="inlineStr">
+      <c r="N52" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 abnormalResults: lấy từ labs.abnormalResult. abnormal phản ánh đúng đánh dấu của nguồn; AI không tự áp ngưỡng.
@@ -6654,22 +6763,29 @@
           <t>"code": item.get("code", "")</t>
         </is>
       </c>
-      <c r="J53" s="26" t="inlineStr">
+      <c r="J53" s="24" t="inlineStr">
+        <is>
+          <t>GỘP diagnosis_primary + diagnosis_comorbidities
+→ code ← diagnosisItem.code
+SAU ĐÓ bỏ chẩn đoán trùng theo code hoặc tên gần giống</t>
+        </is>
+      </c>
+      <c r="K53" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K53" s="23" t="inlineStr">
+      <c r="L53" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L53" s="26" t="inlineStr">
+      <c r="M53" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M53" s="26" t="inlineStr">
+      <c r="N53" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 diagnoses: lấy diagnosisPrimary và diagnosisComorbidities; trả code và description, khử trùng lặp theo cặp mã - tên.
@@ -6680,7 +6796,7 @@
                   "description": "Đái tháo đường type 2"</t>
         </is>
       </c>
-      <c r="N53" s="40" t="inlineStr">
+      <c r="O53" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Đối với các trường hợp"Khử trùng theo cặp code-name; không tự diễn giải ICD." : 
@@ -6694,7 +6810,7 @@
 </t>
         </is>
       </c>
-      <c r="O53" s="41" t="inlineStr">
+      <c r="P53" s="41" t="inlineStr">
         <is>
           <t>1.Chỉ xác định dựa trên text
 - Cùng mã E11, tên "Đái tháo đường type 2" vs "ĐTĐ type 2" → giữ cả hai hay gộp? TRẢ LỜI: Gộp thành 1. Vì cùng code = E11 nên key trùng nhau ngay từ vòng lặp đầu tiên phát hiện trùng - bản ghi xuất hiện sau bị loại bỏ hoàn toàn (không merge tên, không hiển thị lại). Chỉ name/description của bản ghi xuất hiện trước (theo thứ tự quét: diagnosis_primary[] trước, diagnosis_comorbidities[] sau; trong cùng mảng thì theo index) được giữ trong response.
@@ -6762,22 +6878,28 @@
 "description": description if description else None</t>
         </is>
       </c>
-      <c r="J54" s="26" t="inlineStr">
+      <c r="J54" s="24" t="inlineStr">
+        <is>
+          <t>description ← diagnosisItem.description
+NẾU rỗng → null; khi gộp trùng thì giữ description có dữ liệu</t>
+        </is>
+      </c>
+      <c r="K54" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K54" s="27" t="inlineStr">
+      <c r="L54" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L54" s="42" t="inlineStr">
+      <c r="M54" s="42" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M54" s="26" t="inlineStr">
+      <c r="N54" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 diagnoses: lấy diagnosisPrimary và diagnosisComorbidities; trả code và description, khử trùng lặp theo cặp mã - tên.
@@ -6788,13 +6910,13 @@
                   "description": "Đái tháo đường type 2"</t>
         </is>
       </c>
-      <c r="N54" s="40" t="inlineStr">
+      <c r="O54" s="40" t="inlineStr">
         <is>
           <t>data.summary.sections[order=3].latestBySpecialty[].diagnoses[].description
 Sẽ tổng hợp thông tin dữ liệu như thế nào, hiện tại em thấy response trả ra luôn luôn rỗng</t>
         </is>
       </c>
-      <c r="O54" s="38" t="inlineStr">
+      <c r="P54" s="38" t="inlineStr">
         <is>
           <t>key trùng nhau ngay từ vòng lặp đầu tiên phát hiện trùng - bản ghi xuất hiện sau bị loại bỏ hoàn toàn (không merge tên, không hiển thị lại). Chỉ name/descriptioncủa bản ghi xuất hiện trước (theo thứ tự quét: diagnosis_primary[] trước, diagnosis_comorbidities[] sau; trong cùng mảng thì theo index) được giữ trong response.
 Trường hợp "Sẽ tổng hợp thông tin dữ liệu như thế nào, hiện tại em thấy response trả ra luôn luôn rỗng" =&gt; Em check request nếu rỗng thì trả ra rỗng, chị truyền thì description vẫn trả ra nha.</t>
@@ -6852,22 +6974,28 @@
           <t>"name": item.get("name", "")</t>
         </is>
       </c>
-      <c r="J55" s="26" t="inlineStr">
+      <c r="J55" s="24" t="inlineStr">
+        <is>
+          <t>name ← diagnosisItem.name
+SAU ĐÓ bỏ chẩn đoán trùng theo code hoặc tên gần giống</t>
+        </is>
+      </c>
+      <c r="K55" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K55" s="23" t="inlineStr">
+      <c r="L55" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L55" s="26" t="inlineStr">
+      <c r="M55" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M55" s="26" t="inlineStr">
+      <c r="N55" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 diagnoses: lấy diagnosisPrimary và diagnosisComorbidities; trả code và description, khử trùng lặp theo cặp mã - tên.
@@ -6878,13 +7006,13 @@
 Ghi chú đối chiếu (không phải trích dẫn PRD): PRD chỉ quy định code và description cho diagnoses; không có field name riêng ở output.</t>
         </is>
       </c>
-      <c r="N55" s="40" t="inlineStr">
+      <c r="O55" s="40" t="inlineStr">
         <is>
           <t>1.data.summary.sections[order=3].latestBySpecialty[].diagnoses[].name có sử dụng AI hay không
 Giống câu hỏi số 52</t>
         </is>
       </c>
-      <c r="O55" s="38" t="inlineStr">
+      <c r="P55" s="38" t="inlineStr">
         <is>
           <t>key trùng nhau ngay từ vòng lặp đầu tiên phát hiện trùng - bản ghi xuất hiện sau bị loại bỏ hoàn toàn (không merge tên, không hiển thị lại). Chỉ name/descriptioncủa bản ghi xuất hiện trước (theo thứ tự quét: diagnosis_primary[] trước, diagnosis_comorbidities[] sau; trong cùng mảng thì theo index) được giữ trong response.</t>
         </is>
@@ -6940,22 +7068,28 @@
 treatment_sel = _build_treatment(v_plan_sel)</t>
         </is>
       </c>
-      <c r="J56" s="26" t="inlineStr">
+      <c r="J56" s="24" t="inlineStr">
+        <is>
+          <t>TÁCH plan.treatment_plan theo dấu ';'
+Bỏ phần rỗng/vô nghĩa, viết hoa đầu câu → treatment[]</t>
+        </is>
+      </c>
+      <c r="K56" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K56" s="23" t="inlineStr">
+      <c r="L56" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L56" s="26" t="inlineStr">
+      <c r="M56" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M56" s="26" t="inlineStr">
+      <c r="N56" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 treatment và advice: treatment lấy từ plan.treatmentPlan; advice lấy từ plan.doctorAdvice. Đơn thuốc được xử lý tại byPrescription và timeline.details.prescription, không dùng để tạo nhận định điều trị mới.
@@ -7016,22 +7150,29 @@
     advice_sel.append(format_sentence(advice_text))</t>
         </is>
       </c>
-      <c r="J57" s="45" t="inlineStr">
+      <c r="J57" s="44" t="inlineStr">
+        <is>
+          <t>NẾU plan.doctor_advice không rỗng/vô nghĩa
+→ advice ← [doctor_advice đã viết hoa đầu câu]
+NGƯỢC LẠI → []</t>
+        </is>
+      </c>
+      <c r="K57" s="45" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K57" s="43" t="inlineStr">
+      <c r="L57" s="43" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L57" s="26" t="inlineStr">
+      <c r="M57" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M57" s="45" t="inlineStr">
+      <c r="N57" s="45" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 treatment và advice: treatment lấy từ plan.treatmentPlan; advice lấy từ plan.doctorAdvice. Đơn thuốc được xử lý tại byPrescription và timeline.details.prescription, không dùng để tạo nhận định điều trị mới.
@@ -7089,22 +7230,29 @@
           <t>"trends": _compute_trends(v_sel, visits)</t>
         </is>
       </c>
-      <c r="J58" s="26" t="inlineStr">
+      <c r="J58" s="24" t="inlineStr">
+        <is>
+          <t>TÌM lượt cũ gần nhất có cùng specialty
+SO SÁNH blood_pressure, weight_kg và paraclinical_result
+CHỈ tạo trend khi cả hai lượt có dữ liệu và giá trị thay đổi</t>
+        </is>
+      </c>
+      <c r="K58" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K58" s="27" t="inlineStr">
+      <c r="L58" s="27" t="inlineStr">
         <is>
           <t>Không chắc</t>
         </is>
       </c>
-      <c r="L58" s="46" t="inlineStr">
+      <c r="M58" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M58" s="26" t="inlineStr">
+      <c r="N58" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 trends: với mỗi khối, chỉ so sánh chỉ số của lượt đó với lượt trước cùng specialty khi có đủ hai mốc; trả name, from, fromDate, to và toDate.
@@ -7118,12 +7266,12 @@
                   "toDate": "2026-03-21"</t>
         </is>
       </c>
-      <c r="N58" s="40" t="inlineStr">
+      <c r="O58" s="40" t="inlineStr">
         <is>
           <t>logic mapping cụ thể từ input tới output?</t>
         </is>
       </c>
-      <c r="O58" s="41" t="inlineStr">
+      <c r="P58" s="41" t="inlineStr">
         <is>
           <t>Huyết áp / Cân nặng
 latest = chính visit của visit đang được xem xét.
@@ -7186,22 +7334,27 @@
 "name": current_name  # cận lâm sàng</t>
         </is>
       </c>
-      <c r="J59" s="26" t="inlineStr">
+      <c r="J59" s="24" t="inlineStr">
+        <is>
+          <t>trend.name ← 'Huyết áp'/'Cân nặng' hoặc tên xét nghiệm trùng nhau.</t>
+        </is>
+      </c>
+      <c r="K59" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K59" s="27" t="inlineStr">
+      <c r="L59" s="27" t="inlineStr">
         <is>
           <t>Không chắc</t>
         </is>
       </c>
-      <c r="L59" s="26" t="inlineStr">
+      <c r="M59" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M59" s="26" t="inlineStr">
+      <c r="N59" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 trends: với mỗi khối, chỉ so sánh chỉ số của lượt đó với lượt trước cùng specialty khi có đủ hai mốc; trả name, from, fromDate, to và toDate.
@@ -7263,22 +7416,27 @@
 "from": previous_value  # cận lâm sàng</t>
         </is>
       </c>
-      <c r="J60" s="26" t="inlineStr">
+      <c r="J60" s="24" t="inlineStr">
+        <is>
+          <t>trend.from ← giá trị ở lượt cũ gần nhất cùng specialty.</t>
+        </is>
+      </c>
+      <c r="K60" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K60" s="23" t="inlineStr">
+      <c r="L60" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L60" s="26" t="inlineStr">
+      <c r="M60" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M60" s="26" t="inlineStr">
+      <c r="N60" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 trends: với mỗi khối, chỉ so sánh chỉ số của lượt đó với lượt trước cùng specialty khi có đủ hai mốc; trả name, from, fromDate, to và toDate.
@@ -7338,22 +7496,27 @@
           <t>"fromDate": previous_visit.get("visit_date", "")</t>
         </is>
       </c>
-      <c r="J61" s="26" t="inlineStr">
+      <c r="J61" s="24" t="inlineStr">
+        <is>
+          <t>trend.fromDate ← visit_date của lượt cũ gần nhất cùng specialty.</t>
+        </is>
+      </c>
+      <c r="K61" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K61" s="23" t="inlineStr">
+      <c r="L61" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L61" s="26" t="inlineStr">
+      <c r="M61" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M61" s="26" t="inlineStr">
+      <c r="N61" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 trends: với mỗi khối, chỉ so sánh chỉ số của lượt đó với lượt trước cùng specialty khi có đủ hai mốc; trả name, from, fromDate, to và toDate.
@@ -7414,22 +7577,27 @@
 "to": current_value  # cận lâm sàng</t>
         </is>
       </c>
-      <c r="J62" s="26" t="inlineStr">
+      <c r="J62" s="24" t="inlineStr">
+        <is>
+          <t>trend.to ← giá trị ở lượt hiện tại.</t>
+        </is>
+      </c>
+      <c r="K62" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K62" s="23" t="inlineStr">
+      <c r="L62" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L62" s="26" t="inlineStr">
+      <c r="M62" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M62" s="26" t="inlineStr">
+      <c r="N62" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 trends: với mỗi khối, chỉ so sánh chỉ số của lượt đó với lượt trước cùng specialty khi có đủ hai mốc; trả name, from, fromDate, to và toDate.
@@ -7488,22 +7656,27 @@
           <t>"toDate": current_visit.get("visit_date", "")</t>
         </is>
       </c>
-      <c r="J63" s="26" t="inlineStr">
+      <c r="J63" s="24" t="inlineStr">
+        <is>
+          <t>trend.toDate ← visit_date của lượt hiện tại.</t>
+        </is>
+      </c>
+      <c r="K63" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K63" s="23" t="inlineStr">
+      <c r="L63" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L63" s="26" t="inlineStr">
+      <c r="M63" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M63" s="26" t="inlineStr">
+      <c r="N63" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 trends: với mỗi khối, chỉ so sánh chỉ số của lượt đó với lượt trước cùng specialty khi có đủ hai mốc; trả name, from, fromDate, to và toDate.
@@ -7549,29 +7722,24 @@
       </c>
       <c r="G64" s="24" t="inlineStr"/>
       <c r="H64" s="24" t="n"/>
-      <c r="I64" s="69" t="inlineStr">
-        <is>
-          <t>follow_up_items = _ai_list_if(
-    _get_follow_up_items_ai_inputs(selected_visits, now)
-)</t>
-        </is>
-      </c>
-      <c r="J64" s="26" t="inlineStr">
+      <c r="I64" s="69" t="n"/>
+      <c r="J64" s="24" t="n"/>
+      <c r="K64" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K64" s="23" t="inlineStr">
+      <c r="L64" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L64" s="26" t="inlineStr">
+      <c r="M64" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M64" s="26" t="inlineStr">
+      <c r="N64" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.6.1
 Nguồn gồm plan.doctorAdvice và plan.treatmentPlan của lượt gần nhất và các lượt có đơn còn hiệu lực, cùng prescriptions[].doctorNote của các đơn còn hiệu lực.
@@ -7642,22 +7810,29 @@
         })</t>
         </is>
       </c>
-      <c r="J65" s="26" t="inlineStr">
+      <c r="J65" s="24" t="inlineStr">
+        <is>
+          <t>CHO MỖI selectedVisit có followup_date
+→ tạo {specialty, date, valid, note}
+Bỏ trùng theo specialty + date</t>
+        </is>
+      </c>
+      <c r="K65" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K65" s="23" t="inlineStr">
+      <c r="L65" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L65" s="26" t="inlineStr">
+      <c r="M65" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M65" s="26" t="inlineStr">
+      <c r="N65" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.6.2
 Trả từng lịch hẹn có trong plan.followupDate của các lượt được chọn; mỗi phần tử có specialty, date, valid và note. Chỉ khử trùng lặp khi specialty và date giống nhau.
@@ -7717,22 +7892,27 @@
           <t>"specialty": lv.get("specialty", "")</t>
         </is>
       </c>
-      <c r="J66" s="26" t="inlineStr">
+      <c r="J66" s="24" t="inlineStr">
+        <is>
+          <t>followUp.specialty ← selectedVisit.specialty</t>
+        </is>
+      </c>
+      <c r="K66" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K66" s="23" t="inlineStr">
+      <c r="L66" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L66" s="26" t="inlineStr">
+      <c r="M66" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M66" s="26" t="inlineStr">
+      <c r="N66" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 3.1 — R13
 Đa chuyên khoa: one-liner dùng chung; latestBySpecialty chứa lượt gần nhất và các lượt có đơn thuốc còn hiệu lực; thuốc giữ specialty của đơn; followUp giữ specialty của lịch hẹn; trends và changesFromPrevious chỉ so sánh các lượt cùng chuyên khoa.
@@ -7792,22 +7972,27 @@
 "date": normalized_fu_date</t>
         </is>
       </c>
-      <c r="J67" s="26" t="inlineStr">
+      <c r="J67" s="24" t="inlineStr">
+        <is>
+          <t>followUp.date ← chuẩn hóa plan.followup_date thành YYYY-MM-DD; sai ngày → ''</t>
+        </is>
+      </c>
+      <c r="K67" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K67" s="23" t="inlineStr">
+      <c r="L67" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L67" s="26" t="inlineStr">
+      <c r="M67" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M67" s="26" t="inlineStr">
+      <c r="N67" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.6.2
 Trả từng lịch hẹn có trong plan.followupDate của các lượt được chọn; mỗi phần tử có specialty, date, valid và note. Chỉ khử trùng lặp khi specialty và date giống nhau.
@@ -7875,22 +8060,28 @@
 )</t>
         </is>
       </c>
-      <c r="J68" s="26" t="inlineStr">
+      <c r="J68" s="24" t="inlineStr">
+        <is>
+          <t>valid ← TRUE khi followup_date và visit_date đều hợp lệ
+VÀ followup_date &gt; visit_date; còn lại FALSE</t>
+        </is>
+      </c>
+      <c r="K68" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K68" s="23" t="inlineStr">
+      <c r="L68" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L68" s="26" t="inlineStr">
+      <c r="M68" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M68" s="26" t="inlineStr">
+      <c r="N68" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.6.3
 valid=true khi date đọc được và lớn hơn visitDate của phiếu ghi hẹn. Nếu ngày đã qua tại thời điểm tạo summary thì vẫn giữ valid=true và ghi 'Quá hạn' trong note.
@@ -7953,22 +8144,30 @@
     fu_note = "Quá hạn"</t>
         </is>
       </c>
-      <c r="J69" s="26" t="inlineStr">
+      <c r="J69" s="24" t="inlineStr">
+        <is>
+          <t>note ← 'Không đủ dữ liệu...' nếu ngày không parse được
+note ← 'Quá hạn' nếu ngày hẹn hợp lệ nhưng trước hôm nay
+note ← 'Ngày hẹn không hợp lệ...' nếu ngày hẹn ≤ ngày khám
+còn lại note ← ''</t>
+        </is>
+      </c>
+      <c r="K69" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K69" s="23" t="inlineStr">
+      <c r="L69" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L69" s="26" t="inlineStr">
+      <c r="M69" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M69" s="26" t="inlineStr">
+      <c r="N69" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.6.3
 valid=true khi date đọc được và lớn hơn visitDate của phiếu ghi hẹn. Nếu ngày đã qua tại thời điểm tạo summary thì vẫn giữ valid=true và ghi 'Quá hạn' trong note.
@@ -8008,29 +8207,24 @@
       </c>
       <c r="G70" s="24" t="inlineStr"/>
       <c r="H70" s="24" t="n"/>
-      <c r="I70" s="69" t="inlineStr">
-        <is>
-          <t>timeline = []
-for visit in visits:
-    timeline.append({...})</t>
-        </is>
-      </c>
-      <c r="J70" s="26" t="inlineStr">
+      <c r="I70" s="69" t="n"/>
+      <c r="J70" s="24" t="n"/>
+      <c r="K70" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K70" s="23" t="inlineStr">
+      <c r="L70" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L70" s="26" t="inlineStr">
+      <c r="M70" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M70" s="26" t="inlineStr">
+      <c r="N70" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 Mọi lượt khám hợp lệ xuất hiện trong timeline, ghi rõ visitDate, specialty và visitCode; sắp xếp visitDate giảm dần.
@@ -8086,22 +8280,27 @@
           <t>"visitDate": v.get("visit_date", "")</t>
         </is>
       </c>
-      <c r="J71" s="26" t="inlineStr">
+      <c r="J71" s="24" t="inlineStr">
+        <is>
+          <t>timeline.visitDate ← visit.visit_date</t>
+        </is>
+      </c>
+      <c r="K71" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K71" s="23" t="inlineStr">
+      <c r="L71" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L71" s="26" t="inlineStr">
+      <c r="M71" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M71" s="26" t="inlineStr">
+      <c r="N71" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 Mọi lượt khám hợp lệ xuất hiện trong timeline, ghi rõ visitDate, specialty và visitCode; sắp xếp visitDate giảm dần.
@@ -8157,22 +8356,27 @@
           <t>"specialty": v.get("specialty", "")</t>
         </is>
       </c>
-      <c r="J72" s="26" t="inlineStr">
+      <c r="J72" s="24" t="inlineStr">
+        <is>
+          <t>timeline.specialty ← visit.specialty</t>
+        </is>
+      </c>
+      <c r="K72" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K72" s="23" t="inlineStr">
+      <c r="L72" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L72" s="26" t="inlineStr">
+      <c r="M72" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M72" s="26" t="inlineStr">
+      <c r="N72" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 Mọi lượt khám hợp lệ xuất hiện trong timeline, ghi rõ visitDate, specialty và visitCode; sắp xếp visitDate giảm dần.
@@ -8228,22 +8432,27 @@
           <t>"visitCode": v.get("visit_code", "")</t>
         </is>
       </c>
-      <c r="J73" s="26" t="inlineStr">
+      <c r="J73" s="24" t="inlineStr">
+        <is>
+          <t>timeline.visitCode ← visit.visit_code</t>
+        </is>
+      </c>
+      <c r="K73" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K73" s="23" t="inlineStr">
+      <c r="L73" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L73" s="26" t="inlineStr">
+      <c r="M73" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M73" s="26" t="inlineStr">
+      <c r="N73" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 Mọi lượt khám hợp lệ xuất hiện trong timeline, ghi rõ visitDate, specialty và visitCode; sắp xếp visitDate giảm dần.
@@ -8283,27 +8492,24 @@
       </c>
       <c r="G74" s="24" t="inlineStr"/>
       <c r="H74" s="24" t="n"/>
-      <c r="I74" s="69" t="inlineStr">
-        <is>
-          <t>"summary": _ai_str_if(_get_timeline_summary_ai_inputs(v))</t>
-        </is>
-      </c>
-      <c r="J74" s="26" t="inlineStr">
+      <c r="I74" s="69" t="n"/>
+      <c r="J74" s="24" t="n"/>
+      <c r="K74" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K74" s="27" t="inlineStr">
+      <c r="L74" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L74" s="23" t="inlineStr">
+      <c r="M74" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M74" s="26" t="inlineStr">
+      <c r="N74" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.9 — Mỗi mốc lượt khám
 visitDate, specialty, visitCode, summary; details gồm clinical, paraclinical, diagnosis, treatment, prescription, specialtyFindings, changesFromPrevious và advice.
@@ -8348,27 +8554,24 @@
       </c>
       <c r="G75" s="24" t="inlineStr"/>
       <c r="H75" s="24" t="n"/>
-      <c r="I75" s="69" t="inlineStr">
-        <is>
-          <t>"clinical": _ai_str_if(_get_timeline_clinical_ai_inputs(v))</t>
-        </is>
-      </c>
-      <c r="J75" s="26" t="inlineStr">
+      <c r="I75" s="69" t="n"/>
+      <c r="J75" s="24" t="n"/>
+      <c r="K75" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K75" s="27" t="inlineStr">
+      <c r="L75" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L75" s="23" t="inlineStr">
+      <c r="M75" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M75" s="26" t="inlineStr">
+      <c r="N75" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 details.clinical theo thứ tự: bệnh sử -&gt; dấu hiệu sinh tồn -&gt; khám thực thể; chỉ dùng dữ liệu của đúng lượt.
@@ -8410,30 +8613,24 @@
       </c>
       <c r="G76" s="24" t="inlineStr"/>
       <c r="H76" s="24" t="n"/>
-      <c r="I76" s="69" t="inlineStr">
-        <is>
-          <t>"paraclinical": _ai_list_if(
-    (v.get("labs") or {}).get("paraclinical_result")
-)
-# mapper.py không dựng riêng paraclinical[].name.</t>
-        </is>
-      </c>
-      <c r="J76" s="26" t="inlineStr">
+      <c r="I76" s="69" t="n"/>
+      <c r="J76" s="24" t="n"/>
+      <c r="K76" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K76" s="27" t="inlineStr">
+      <c r="L76" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L76" s="23" t="inlineStr">
+      <c r="M76" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M76" s="26" t="inlineStr">
+      <c r="N76" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 Kết quả không nằm trong labs.abnormalResult không đưa vào abnormalResults; nội dung cận lâm sàng của lượt vẫn nằm trong timeline.details.paraclinical.
@@ -8480,30 +8677,24 @@
       </c>
       <c r="G77" s="24" t="inlineStr"/>
       <c r="H77" s="24" t="n"/>
-      <c r="I77" s="69" t="inlineStr">
-        <is>
-          <t>"paraclinical": _ai_list_if(
-    (v.get("labs") or {}).get("paraclinical_result")
-)
-# mapper.py không dựng riêng paraclinical[].result.</t>
-        </is>
-      </c>
-      <c r="J77" s="26" t="inlineStr">
+      <c r="I77" s="69" t="n"/>
+      <c r="J77" s="24" t="n"/>
+      <c r="K77" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K77" s="27" t="inlineStr">
+      <c r="L77" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L77" s="23" t="inlineStr">
+      <c r="M77" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M77" s="26" t="inlineStr">
+      <c r="N77" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.5.2
 Kết quả không nằm trong labs.abnormalResult không đưa vào abnormalResults; nội dung cận lâm sàng của lượt vẫn nằm trong timeline.details.paraclinical.
@@ -8568,22 +8759,28 @@
           <t>"code": item.get("code", "")</t>
         </is>
       </c>
-      <c r="J78" s="26" t="inlineStr">
+      <c r="J78" s="24" t="inlineStr">
+        <is>
+          <t>GỘP diagnosis_primary + diagnosis_comorbidities của visit
+→ diagnosis.code ← diagnosisItem.code; sau đó bỏ trùng</t>
+        </is>
+      </c>
+      <c r="K78" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K78" s="23" t="inlineStr">
+      <c r="L78" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L78" s="26" t="inlineStr">
+      <c r="M78" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M78" s="26" t="inlineStr">
+      <c r="N78" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 prescription, paraclinical, diagnosis, treatment, specialtyFindings và advice lấy từ đúng lượt; field không có dữ liệu dùng giá trị rỗng đúng contract.
@@ -8644,22 +8841,28 @@
 "description": description if description else None</t>
         </is>
       </c>
-      <c r="J79" s="26" t="inlineStr">
+      <c r="J79" s="24" t="inlineStr">
+        <is>
+          <t>diagnosis.description ← diagnosisItem.description
+NẾU rỗng → null; không lấy diagnosis_text trong code hiện tại</t>
+        </is>
+      </c>
+      <c r="K79" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K79" s="23" t="inlineStr">
+      <c r="L79" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L79" s="26" t="inlineStr">
+      <c r="M79" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M79" s="26" t="inlineStr">
+      <c r="N79" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 prescription, paraclinical, diagnosis, treatment, specialtyFindings và advice lấy từ đúng lượt; field không có dữ liệu dùng giá trị rỗng đúng contract.
@@ -8718,22 +8921,27 @@
           <t>"name": item.get("name", "")</t>
         </is>
       </c>
-      <c r="J80" s="26" t="inlineStr">
+      <c r="J80" s="24" t="inlineStr">
+        <is>
+          <t>diagnosis.name ← diagnosisItem.name; sau đó bỏ trùng theo code/tên.</t>
+        </is>
+      </c>
+      <c r="K80" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K80" s="23" t="inlineStr">
+      <c r="L80" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L80" s="26" t="inlineStr">
+      <c r="M80" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M80" s="26" t="inlineStr">
+      <c r="N80" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 5
 Payload dưới đây là template cấu trúc response đã chốt. Giá trị chỉ để minh họa và không phải expected output của input tại mục 2.5. Không bổ sung field ngoài contract.
@@ -8793,22 +9001,28 @@
           <t>v_treatment = _build_treatment(v_plan, split_items=False)</t>
         </is>
       </c>
-      <c r="J81" s="26" t="inlineStr">
+      <c r="J81" s="24" t="inlineStr">
+        <is>
+          <t>LẤY toàn bộ plan.treatment_plan làm một phần tử treatment[]
+Không tách theo dấu ';'; bỏ nếu rỗng/vô nghĩa</t>
+        </is>
+      </c>
+      <c r="K81" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K81" s="23" t="inlineStr">
+      <c r="L81" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L81" s="26" t="inlineStr">
+      <c r="M81" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M81" s="26" t="inlineStr">
+      <c r="N81" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 prescription, paraclinical, diagnosis, treatment, specialtyFindings và advice lấy từ đúng lượt; field không có dữ liệu dùng giá trị rỗng đúng contract.
@@ -8876,22 +9090,29 @@
           <t>v_presc = _build_prescription_summaries(v)</t>
         </is>
       </c>
-      <c r="J82" s="45" t="inlineStr">
+      <c r="J82" s="44" t="inlineStr">
+        <is>
+          <t>CHO MỖI item trong prescriptions[] của chính visit
+Bỏ item không có name
+Tạo chuỗi: name + tần suất rút gọn + (duration)</t>
+        </is>
+      </c>
+      <c r="K82" s="45" t="inlineStr">
         <is>
           <t>Hiện tại chỉ sử phần visits[].prescriptions[] được lấy từ OH thôi ạ</t>
         </is>
       </c>
-      <c r="K82" s="47" t="inlineStr">
+      <c r="L82" s="47" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L82" s="45" t="inlineStr">
+      <c r="M82" s="45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M82" s="45" t="inlineStr">
+      <c r="N82" s="45" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 prescription, paraclinical, diagnosis, treatment, specialtyFindings và advice lấy từ đúng lượt; field không có dữ liệu dùng giá trị rỗng đúng contract.
@@ -8908,12 +9129,12 @@
 Ghi chú đối chiếu (không phải trích dẫn PRD): PRD không nêu quy tắc ưu tiên/đối chiếu chi tiết giữa plan.prescription và prescriptions[] khi hai nguồn khác nhau</t>
         </is>
       </c>
-      <c r="N82" s="40" t="inlineStr">
+      <c r="O82" s="40" t="inlineStr">
         <is>
           <t>logic mapping cụ thể từ input tới output?</t>
         </is>
       </c>
-      <c r="O82" s="48" t="inlineStr">
+      <c r="P82" s="48" t="inlineStr">
         <is>
           <t>Dựa vào đơn thuốc trong visit chỉ lấy name (double check với PRD thì phần trả ra đang xót, thiếu dosageInstruction (liều và cách dùng, nguyên văn), route, quantity, duration, note)</t>
         </is>
@@ -8950,27 +9171,24 @@
       </c>
       <c r="G83" s="24" t="inlineStr"/>
       <c r="H83" s="24" t="n"/>
-      <c r="I83" s="69" t="inlineStr">
-        <is>
-          <t>"obstetrics": _build_obstetrics(v)</t>
-        </is>
-      </c>
-      <c r="J83" s="26" t="inlineStr">
+      <c r="I83" s="69" t="n"/>
+      <c r="J83" s="24" t="n"/>
+      <c r="K83" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K83" s="27" t="inlineStr">
+      <c r="L83" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L83" s="23" t="inlineStr">
+      <c r="M83" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M83" s="26" t="inlineStr">
+      <c r="N83" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 prescription, paraclinical, diagnosis, treatment, specialtyFindings và advice lấy từ đúng lượt; field không có dữ liệu dùng giá trị rỗng đúng contract.
@@ -9035,22 +9253,28 @@
 "nutrition": exam.get("nutrition_assessment") or exam.get("nutrition assessment") or ""</t>
         </is>
       </c>
-      <c r="J84" s="26" t="inlineStr">
+      <c r="J84" s="24" t="inlineStr">
+        <is>
+          <t>nutrition ← examination.nutrition_assessment hoặc key có dấu cách
+Lưu ý: code không kiểm tra specialty Nhi.</t>
+        </is>
+      </c>
+      <c r="K84" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K84" s="23" t="inlineStr">
+      <c r="L84" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L84" s="26" t="inlineStr">
+      <c r="M84" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M84" s="26" t="inlineStr">
+      <c r="N84" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 prescription, paraclinical, diagnosis, treatment, specialtyFindings và advice lấy từ đúng lượt; field không có dữ liệu dùng giá trị rỗng đúng contract.
@@ -9113,22 +9337,28 @@
 "vaccination": exam.get("vaccination_assessment") or exam.get("vaccination assessment") or ""</t>
         </is>
       </c>
-      <c r="J85" s="26" t="inlineStr">
+      <c r="J85" s="24" t="inlineStr">
+        <is>
+          <t>vaccination ← examination.vaccination_assessment hoặc key có dấu cách
+Lưu ý: code không kiểm tra specialty Nhi.</t>
+        </is>
+      </c>
+      <c r="K85" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K85" s="23" t="inlineStr">
+      <c r="L85" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L85" s="26" t="inlineStr">
+      <c r="M85" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M85" s="26" t="inlineStr">
+      <c r="N85" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 prescription, paraclinical, diagnosis, treatment, specialtyFindings và advice lấy từ đúng lượt; field không có dữ liệu dùng giá trị rỗng đúng contract.
@@ -9191,22 +9421,28 @@
 "motorDevelopment": exam.get("motor_development") or exam.get("motor development") or ""</t>
         </is>
       </c>
-      <c r="J86" s="26" t="inlineStr">
+      <c r="J86" s="24" t="inlineStr">
+        <is>
+          <t>motorDevelopment ← examination.motor_development hoặc key có dấu cách
+Lưu ý: code không kiểm tra specialty Nhi.</t>
+        </is>
+      </c>
+      <c r="K86" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K86" s="23" t="inlineStr">
+      <c r="L86" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L86" s="26" t="inlineStr">
+      <c r="M86" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M86" s="26" t="inlineStr">
+      <c r="N86" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 prescription, paraclinical, diagnosis, treatment, specialtyFindings và advice lấy từ đúng lượt; field không có dữ liệu dùng giá trị rỗng đúng contract.
@@ -9269,22 +9505,28 @@
 "mentalDevelopment": exam.get("mental_development") or exam.get("mental development") or ""</t>
         </is>
       </c>
-      <c r="J87" s="26" t="inlineStr">
+      <c r="J87" s="24" t="inlineStr">
+        <is>
+          <t>mentalDevelopment ← examination.mental_development hoặc key có dấu cách
+Lưu ý: code không kiểm tra specialty Nhi.</t>
+        </is>
+      </c>
+      <c r="K87" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K87" s="23" t="inlineStr">
+      <c r="L87" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L87" s="26" t="inlineStr">
+      <c r="M87" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M87" s="26" t="inlineStr">
+      <c r="N87" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 prescription, paraclinical, diagnosis, treatment, specialtyFindings và advice lấy từ đúng lượt; field không có dữ liệu dùng giá trị rỗng đúng contract.
@@ -9328,27 +9570,24 @@
       </c>
       <c r="G88" s="24" t="inlineStr"/>
       <c r="H88" s="24" t="n"/>
-      <c r="I88" s="69" t="inlineStr">
-        <is>
-          <t>"changesFromPrevious": _get_changes_from_previous_ai_value(v, visits)</t>
-        </is>
-      </c>
-      <c r="J88" s="26" t="inlineStr">
+      <c r="I88" s="69" t="n"/>
+      <c r="J88" s="24" t="n"/>
+      <c r="K88" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K88" s="27" t="inlineStr">
+      <c r="L88" s="27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L88" s="23" t="inlineStr">
+      <c r="M88" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M88" s="26" t="inlineStr">
+      <c r="N88" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 changesFromPrevious chỉ so với lượt trước cùng specialty và chỉ ghi thay đổi truy vết được; không có mốc trước cùng specialty thì trả [].
@@ -9391,27 +9630,24 @@
       </c>
       <c r="G89" s="24" t="inlineStr"/>
       <c r="H89" s="24" t="n"/>
-      <c r="I89" s="69" t="inlineStr">
-        <is>
-          <t>"advice": _ai_list_if(_get_timeline_advice_ai_inputs(v))</t>
-        </is>
-      </c>
-      <c r="J89" s="26" t="inlineStr">
+      <c r="I89" s="69" t="n"/>
+      <c r="J89" s="24" t="n"/>
+      <c r="K89" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K89" s="23" t="inlineStr">
+      <c r="L89" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L89" s="26" t="inlineStr">
+      <c r="M89" s="26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M89" s="26" t="inlineStr">
+      <c r="N89" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.7
 prescription, paraclinical, diagnosis, treatment, specialtyFindings và advice lấy từ đúng lượt; field không có dữ liệu dùng giá trị rỗng đúng contract.
@@ -9480,22 +9716,27 @@
           <t>"errors": {}</t>
         </is>
       </c>
-      <c r="J90" s="26" t="inlineStr">
+      <c r="J90" s="24" t="inlineStr">
+        <is>
+          <t>errors ← {}  (code hiện luôn trả object rỗng)</t>
+        </is>
+      </c>
+      <c r="K90" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K90" s="23" t="inlineStr">
+      <c r="L90" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L90" s="26" t="inlineStr">
+      <c r="M90" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M90" s="26" t="inlineStr">
+      <c r="N90" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 5
   "errors": {}
@@ -9535,22 +9776,27 @@
           <t># patient.pseudo_id không được tham chiếu trong mapper.py.</t>
         </is>
       </c>
-      <c r="J91" s="26" t="inlineStr">
+      <c r="J91" s="24" t="inlineStr">
+        <is>
+          <t>KHÔNG DÙNG patient.pseudo_id trong mapper.py → không có output trực tiếp.</t>
+        </is>
+      </c>
+      <c r="K91" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K91" s="23" t="inlineStr">
+      <c r="L91" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L91" s="26" t="inlineStr">
+      <c r="M91" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M91" s="26" t="inlineStr">
+      <c r="N91" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.5 — input
   "patient": { "pseudoId": "1ae82d07...70d8", "age": 79, "gender": "male" },
@@ -9594,22 +9840,27 @@
           <t># visits[].clinic không được tham chiếu trong mapper.py.</t>
         </is>
       </c>
-      <c r="J92" s="26" t="inlineStr">
+      <c r="J92" s="24" t="inlineStr">
+        <is>
+          <t>KHÔNG DÙNG visits[].clinic trong mapper.py → không có output trực tiếp.</t>
+        </is>
+      </c>
+      <c r="K92" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K92" s="23" t="inlineStr">
+      <c r="L92" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L92" s="26" t="inlineStr">
+      <c r="M92" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M92" s="26" t="inlineStr">
+      <c r="N92" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.2
 clinic
@@ -9656,22 +9907,28 @@
           <t># current_medications[].last_dose_date không được tham chiếu trong mapper.py.</t>
         </is>
       </c>
-      <c r="J93" s="26" t="inlineStr">
+      <c r="J93" s="24" t="inlineStr">
+        <is>
+          <t>KHÔNG DÙNG current_medications[].last_dose_date trong mapper.py
+→ không có output trực tiếp.</t>
+        </is>
+      </c>
+      <c r="K93" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K93" s="23" t="inlineStr">
+      <c r="L93" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L93" s="26" t="inlineStr">
+      <c r="M93" s="26" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="M93" s="26" t="inlineStr">
+      <c r="N93" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 4.4
 selfReported: lấy từ history.currentMedications[]; trả name, dosage, route và askedDate. askedDate là visitDate của phiếu ghi nhận. lastDoseDate không có field tương ứng trong response và không được tự gộp vào field khác.</t>
@@ -9710,22 +9967,27 @@
           <t># prescriptions[].prescriber không được tham chiếu trong mapper.py.</t>
         </is>
       </c>
-      <c r="J94" s="26" t="inlineStr">
+      <c r="J94" s="24" t="inlineStr">
+        <is>
+          <t>KHÔNG DÙNG prescriptions[].prescriber trong mapper.py → không có output trực tiếp.</t>
+        </is>
+      </c>
+      <c r="K94" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K94" s="23" t="inlineStr">
+      <c r="L94" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L94" s="26" t="inlineStr">
+      <c r="M94" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M94" s="26" t="inlineStr">
+      <c r="N94" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.4
 prescriber
@@ -9772,22 +10034,28 @@
 # Giá trị này hiện chỉ đi vào bộ input AI của oneLiner.</t>
         </is>
       </c>
-      <c r="J95" s="26" t="inlineStr">
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>diagnosis_on_prescription được gom vào dữ liệu đầu vào AI của oneLiner
+Code hiện không dùng nó cho Tiền sử nền hoặc Timeline.</t>
+        </is>
+      </c>
+      <c r="K95" s="26" t="inlineStr">
         <is>
           <t>Vẫn sử dụng trong đầu vào của oneliner, Tiền sử nền, Timeline</t>
         </is>
       </c>
-      <c r="K95" s="23" t="inlineStr">
+      <c r="L95" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L95" s="26" t="inlineStr">
+      <c r="M95" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M95" s="26" t="inlineStr">
+      <c r="N95" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.4
 diagnosisOnPrescription
@@ -9799,12 +10067,12 @@
 Ghi chú đối chiếu (không phải trích dẫn PRD): diagnosisOnPrescription có trong input nhưng không có field trả trực tiếp. Nguồn diagnoses được mục 4.5.2 chỉ định là diagnosisPrimary và diagnosisComorbidities.</t>
         </is>
       </c>
-      <c r="N95" s="40" t="inlineStr">
+      <c r="O95" s="40" t="inlineStr">
         <is>
           <t>input impact/mapping như nào với các trường/trường con của Tiền sử nền và Timeline?</t>
         </is>
       </c>
-      <c r="O95" s="49" t="inlineStr">
+      <c r="P95" s="49" t="inlineStr">
         <is>
           <t>prompt OneLinerMessages, cụm 1 của oneLiner ("[bệnh nền hoặc tiền sử chính, kèm mốc nếu nguồn có]"). Trong confirm trước dư phần "Tiền sử nền, Timeline"</t>
         </is>
@@ -9846,22 +10114,29 @@
 )</t>
         </is>
       </c>
-      <c r="J96" s="26" t="inlineStr">
+      <c r="J96" s="24" t="inlineStr">
+        <is>
+          <t>stop_date dùng để xác định thuốc còn hạn:
+còn hạn khi parse được ngày VÀ stop_date ≥ hôm nay
+Kết quả ảnh hưởng byPrescription, selectedVisits và followUpItems.</t>
+        </is>
+      </c>
+      <c r="K96" s="26" t="inlineStr">
         <is>
           <t>Có dùng để xét thuốc đó hết hạn chưa</t>
         </is>
       </c>
-      <c r="K96" s="23" t="inlineStr">
+      <c r="L96" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L96" s="26" t="inlineStr">
+      <c r="M96" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M96" s="26" t="inlineStr">
+      <c r="N96" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.5 — input
               "stopDate": "2026-07-21 14:58:03",
@@ -9871,7 +10146,7 @@
 Ghi chú đối chiếu (không phải trích dẫn PRD): PRD có stopDate trong template input nhưng chưa mô tả quy tắc dùng stopDate để tính durationEndDate hoặc quyết định ngừng thuốc.</t>
         </is>
       </c>
-      <c r="N96" s="38" t="inlineStr">
+      <c r="O96" s="38" t="inlineStr">
         <is>
           <t>1. dùng để xác định visit được tóm tắt hay không:
 + stop_date &gt;= ngày hiện tại: có tóm tắt (phần tình trạng bệnh nhận)
@@ -9879,7 +10154,7 @@
 2. để gán vào durationEndDate nếu thuốc được liệt kê trong danh sách thuốc đang sử dụng</t>
         </is>
       </c>
-      <c r="O96" s="38" t="n"/>
+      <c r="P96" s="38" t="n"/>
     </row>
     <row r="97" ht="275.25" customHeight="1">
       <c r="A97" s="23" t="n">
@@ -9909,22 +10184,28 @@
           <t># diagnosis.diagnosis_from_referring_facility không được tham chiếu trong mapper.py.</t>
         </is>
       </c>
-      <c r="J97" s="26" t="inlineStr">
+      <c r="J97" s="24" t="inlineStr">
+        <is>
+          <t>KHÔNG DÙNG diagnosis_from_referring_facility trong mapper.py
+→ không có output trực tiếp.</t>
+        </is>
+      </c>
+      <c r="K97" s="26" t="inlineStr">
         <is>
           <t>Vẫn sử dụng trong đầu vào của oneliner, Tiền sử nền, Timeline</t>
         </is>
       </c>
-      <c r="K97" s="23" t="inlineStr">
+      <c r="L97" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L97" s="26" t="inlineStr">
+      <c r="M97" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M97" s="26" t="inlineStr">
+      <c r="N97" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.5 — khối diagnosis
       "diagnosis": {
@@ -9937,12 +10218,12 @@
 Ghi chú đối chiếu (không phải trích dẫn PRD): Không tìm thấy field diagnosis_from_referring_facility hoặc diagnosisFromReferringFacility trong PRD; chưa có quy định mapping cho field này.</t>
         </is>
       </c>
-      <c r="N97" s="40" t="inlineStr">
+      <c r="O97" s="40" t="inlineStr">
         <is>
           <t>input impact/mapping như nào với các trường/trường con của Tiền sử nền và Timeline?</t>
         </is>
       </c>
-      <c r="O97" s="38" t="inlineStr">
+      <c r="P97" s="38" t="inlineStr">
         <is>
           <t>1. prompt OneLinerMessages, cụm 1 của oneLiner ("[bệnh nền hoặc tiền sử chính, kèm mốc nếu nguồn có]"). 
 2. Dùng để liệt kê thêm bệnh trong tiền sử nền</t>
@@ -10004,22 +10285,29 @@
     })</t>
         </is>
       </c>
-      <c r="J98" s="26" t="inlineStr">
+      <c r="J98" s="24" t="inlineStr">
+        <is>
+          <t>CHO MỖI diagnosis_primary[]
+→ description ← item.description; nếu rỗng → null
+Dùng chung cho latestBySpecialty và timeline.</t>
+        </is>
+      </c>
+      <c r="K98" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K98" s="23" t="inlineStr">
+      <c r="L98" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L98" s="26" t="inlineStr">
+      <c r="M98" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M98" s="26" t="inlineStr">
+      <c r="N98" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.5 — khối diagnosis
       "diagnosis": {
@@ -10092,22 +10380,29 @@
     })</t>
         </is>
       </c>
-      <c r="J99" s="26" t="inlineStr">
+      <c r="J99" s="24" t="inlineStr">
+        <is>
+          <t>CHO MỖI diagnosis_comorbidities[]
+→ description ← item.description; nếu rỗng → null
+Dùng chung cho latestBySpecialty và timeline.</t>
+        </is>
+      </c>
+      <c r="K99" s="26" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="K99" s="23" t="inlineStr">
+      <c r="L99" s="23" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L99" s="26" t="inlineStr">
+      <c r="M99" s="26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M99" s="26" t="inlineStr">
+      <c r="N99" s="26" t="inlineStr">
         <is>
           <t>Nguồn: PRD Patient Summary.docx — Phần II, mục 2.5 — khối diagnosis
       "diagnosis": {
@@ -10135,13 +10430,14 @@
       <c r="G100" s="50" t="n"/>
       <c r="H100" s="51" t="n"/>
       <c r="I100" s="72" t="n"/>
-      <c r="J100" s="50" t="n"/>
+      <c r="J100" s="51" t="n"/>
       <c r="K100" s="50" t="n"/>
       <c r="L100" s="50" t="n"/>
       <c r="M100" s="50" t="n"/>
+      <c r="N100" s="50" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:P99"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Dữ liệu mẫu/Mapping.xlsx
+++ b/Dữ liệu mẫu/Mapping.xlsx
@@ -2948,8 +2948,11 @@
       </c>
       <c r="J2" s="24" t="inlineStr">
         <is>
-          <t>output.request_id ← input.request_id
-NẾU input không có request_id → tạo UUID mới</t>
+          <t>if (isset($input["request_id"])) {
+    $output["request_id"] = $input["request_id"];
+} else {
+    $output["request_id"] = uuid();
+}</t>
         </is>
       </c>
       <c r="K2" s="25" t="inlineStr">
@@ -3025,7 +3028,7 @@
       </c>
       <c r="J3" s="24" t="inlineStr">
         <is>
-          <t>visitCount ← số phần tử trong visits[]</t>
+          <t>$output["visitCount"] = count($visits);</t>
         </is>
       </c>
       <c r="K3" s="26" t="inlineStr">
@@ -3105,8 +3108,12 @@
       </c>
       <c r="J4" s="24" t="inlineStr">
         <is>
-          <t>SẮP XẾP visits theo visit_date mới → cũ
-latestVisitDate ← visit_date của lượt đầu tiên</t>
+          <t>usort($visits, "visitDateDesc");
+if (count($visits) &gt; 0) {
+    $output["latestVisitDate"] = $visits[0]["visit_date"] ?? "";
+} else {
+    $output["latestVisitDate"] = "";
+}</t>
         </is>
       </c>
       <c r="K4" s="26" t="inlineStr">
@@ -3187,8 +3194,13 @@
       </c>
       <c r="J5" s="24" t="inlineStr">
         <is>
-          <t>specialties ← danh sách rỗng
-CHO MỖI visit → thêm specialty nếu khác rỗng và chưa có</t>
+          <t>$output["specialties"] = [];
+foreach ($visits as $visit) {
+    $specialty = $visit["specialty"] ?? "";
+    if ($specialty !== "" &amp;&amp; !in_array($specialty, $output["specialties"])) {
+        $output["specialties"][] = $specialty;
+    }
+}</t>
         </is>
       </c>
       <c r="K5" s="26" t="inlineStr">
@@ -3414,7 +3426,9 @@
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>Code chưa tạo riêng alerts[].type; field này nằm trong placeholder AI của alerts.</t>
+          <t>foreach ($alerts as &amp;$alert) {
+    $alert["type"] = "warning";
+}</t>
         </is>
       </c>
       <c r="K8" s="29" t="inlineStr">
@@ -3781,7 +3795,10 @@
       </c>
       <c r="J14" s="32" t="inlineStr">
         <is>
-          <t>GÁN cố định order của 4 section lần lượt là 1, 2, 3, 4.</t>
+          <t>$section1["order"] = 1;
+$section2["order"] = 2;
+$section3["order"] = 3;
+$section4["order"] = 4;</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr">
@@ -3870,9 +3887,10 @@
       </c>
       <c r="J15" s="32" t="inlineStr">
         <is>
-          <t>GÁN cố định title theo order:
-1 Tiền sử nền; 2 Thuốc đang sử dụng;
-3 Tình trạng bệnh nhân; 4 Việc cần theo dõi tiếp.</t>
+          <t>$section1["title"] = "Tiền sử nền";
+$section2["title"] = "Thuốc đang sử dụng";
+$section3["title"] = "Tình trạng bệnh nhân";
+$section4["title"] = "Việc cần theo dõi tiếp";</t>
         </is>
       </c>
       <c r="K15" s="23" t="inlineStr">
@@ -4269,8 +4287,7 @@
       </c>
       <c r="J21" s="24" t="inlineStr">
         <is>
-          <t>Với thuốc thuộc đơn mới nhất hoặc còn hạn:
-name ← item.name</t>
+          <t>$mappedItem["name"] = $item["name"] ?? "";</t>
         </is>
       </c>
       <c r="K21" s="26" t="inlineStr">
@@ -4357,7 +4374,11 @@
       </c>
       <c r="J22" s="24" t="inlineStr">
         <is>
-          <t>dosage ← tìm cụm số + đơn vị (mg, ml, g, mcg, IU...) trong item.name</t>
+          <t>if (preg_match("/(\d+(?:[.,]\d+)?\s*(?:mcg|mg|ml|g|IU|UI))/i", $item["name"], $match)) {
+    $mappedItem["dosage"] = trim($match[1]);
+} else {
+    $mappedItem["dosage"] = "";
+}</t>
         </is>
       </c>
       <c r="K22" s="26" t="inlineStr">
@@ -4437,7 +4458,7 @@
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
-          <t>frequency ← giữ nguyên toàn bộ item.dosage_instruction; không tách nhỏ.</t>
+          <t>$mappedItem["frequency"] = $item["dosage_instruction"] ?? "";</t>
         </is>
       </c>
       <c r="K23" s="26" t="inlineStr">
@@ -4514,7 +4535,7 @@
       </c>
       <c r="J24" s="24" t="inlineStr">
         <is>
-          <t>quantity ← item.quantity</t>
+          <t>$mappedItem["quantity"] = $item["quantity"] ?? "";</t>
         </is>
       </c>
       <c r="K24" s="26" t="inlineStr">
@@ -4597,7 +4618,7 @@
       </c>
       <c r="J25" s="24" t="inlineStr">
         <is>
-          <t>prescribedDate ← prescription.prescribed_date</t>
+          <t>$mappedItem["prescribedDate"] = $prescription["prescribed_date"] ?? "";</t>
         </is>
       </c>
       <c r="K25" s="26" t="inlineStr">
@@ -4677,7 +4698,7 @@
       </c>
       <c r="J26" s="24" t="inlineStr">
         <is>
-          <t>prescriptionCode ← prescription.prescription_code</t>
+          <t>$mappedItem["prescriptionCode"] = $prescription["prescription_code"] ?? "";</t>
         </is>
       </c>
       <c r="K26" s="26" t="inlineStr">
@@ -4757,7 +4778,7 @@
       </c>
       <c r="J27" s="24" t="inlineStr">
         <is>
-          <t>specialty ← prescription.specialty</t>
+          <t>$mappedItem["specialty"] = $prescription["specialty"] ?? "";</t>
         </is>
       </c>
       <c r="K27" s="26" t="inlineStr">
@@ -4838,7 +4859,7 @@
       </c>
       <c r="J28" s="24" t="inlineStr">
         <is>
-          <t>durationEndDate ← item.stop_date</t>
+          <t>$mappedItem["durationEndDate"] = $item["stop_date"] ?? null;</t>
         </is>
       </c>
       <c r="K28" s="26" t="inlineStr">
@@ -4915,9 +4936,9 @@
       </c>
       <c r="J29" s="24" t="inlineStr">
         <is>
-          <t>CHO MỖI thuốc trong current_medications của lượt mới nhất
-→ name ← medication.name
-Lưu ý: code hiện không kiểm tra medication_status.</t>
+          <t>foreach ($latestVisit["history"]["current_medications"] ?? [] as $medication) {
+    $selfReportedItem["name"] = $medication["name"] ?? "";
+}</t>
         </is>
       </c>
       <c r="K29" s="26" t="inlineStr">
@@ -4997,7 +5018,7 @@
       </c>
       <c r="J30" s="24" t="inlineStr">
         <is>
-          <t>dosage ← medication.dosage của current_medications ở lượt mới nhất.</t>
+          <t>$selfReportedItem["dosage"] = $medication["dosage"] ?? "";</t>
         </is>
       </c>
       <c r="K30" s="26" t="inlineStr">
@@ -5077,7 +5098,7 @@
       </c>
       <c r="J31" s="24" t="inlineStr">
         <is>
-          <t>route ← medication.route của current_medications ở lượt mới nhất.</t>
+          <t>$selfReportedItem["route"] = $medication["route"] ?? "";</t>
         </is>
       </c>
       <c r="K31" s="26" t="inlineStr">
@@ -5157,7 +5178,7 @@
       </c>
       <c r="J32" s="24" t="inlineStr">
         <is>
-          <t>askedDate ← visit_date của lượt khám mới nhất.</t>
+          <t>$selfReportedItem["askedDate"] = $latestVisit["visit_date"] ?? "";</t>
         </is>
       </c>
       <c r="K32" s="26" t="inlineStr">
@@ -5241,9 +5262,13 @@
       </c>
       <c r="J33" s="24" t="inlineStr">
         <is>
-          <t>selectedVisits ← mọi lượt có ngày khám mới nhất toàn cục
-+ các lượt cũ có ít nhất một item.stop_date còn hạn
-SAU ĐÓ bỏ trùng và sắp xếp ngày giảm dần</t>
+          <t>$selectedVisits = $latestVisits;
+foreach ($visits as $visit) {
+    if (!in_array($visit, $selectedVisits) &amp;&amp; hasActivePrescription($visit, $today)) {
+        $selectedVisits[] = $visit;
+    }
+}
+usort($selectedVisits, "visitDateDesc");</t>
         </is>
       </c>
       <c r="K33" s="26" t="inlineStr">
@@ -5326,7 +5351,7 @@
       </c>
       <c r="J34" s="24" t="inlineStr">
         <is>
-          <t>CHO MỖI selectedVisit → visitDate ← selectedVisit.visit_date</t>
+          <t>$latestBySpecialtyItem["visitDate"] = $selectedVisit["visit_date"] ?? "";</t>
         </is>
       </c>
       <c r="K34" s="26" t="inlineStr">
@@ -5401,7 +5426,7 @@
       </c>
       <c r="J35" s="24" t="inlineStr">
         <is>
-          <t>CHO MỖI selectedVisit → specialty ← selectedVisit.specialty</t>
+          <t>$latestBySpecialtyItem["specialty"] = $selectedVisit["specialty"] ?? "";</t>
         </is>
       </c>
       <c r="K35" s="26" t="inlineStr">
@@ -5476,7 +5501,11 @@
       </c>
       <c r="J36" s="24" t="inlineStr">
         <is>
-          <t>pulse ← đổi vitals.pulse thành số; lỗi/rỗng → 0</t>
+          <t>if (is_numeric($vitals["pulse"] ?? null)) {
+    $vitalSigns["pulse"] = 0 + $vitals["pulse"];
+} else {
+    $vitalSigns["pulse"] = 0;
+}</t>
         </is>
       </c>
       <c r="K36" s="26" t="inlineStr">
@@ -5559,7 +5588,7 @@
       </c>
       <c r="J37" s="24" t="inlineStr">
         <is>
-          <t>bloodPressure ← đổi vitals.blood_pressure thành chuỗi.</t>
+          <t>$vitalSigns["bloodPressure"] = (string) ($vitals["blood_pressure"] ?? "");</t>
         </is>
       </c>
       <c r="K37" s="26" t="inlineStr">
@@ -5641,7 +5670,11 @@
       </c>
       <c r="J38" s="24" t="inlineStr">
         <is>
-          <t>spo2 ← đổi vitals.spo2 thành số; lỗi/rỗng → 0</t>
+          <t>if (is_numeric($vitals["spo2"] ?? null)) {
+    $vitalSigns["spo2"] = 0 + $vitals["spo2"];
+} else {
+    $vitalSigns["spo2"] = 0;
+}</t>
         </is>
       </c>
       <c r="K38" s="26" t="inlineStr">
@@ -5723,7 +5756,11 @@
       </c>
       <c r="J39" s="24" t="inlineStr">
         <is>
-          <t>respiratoryRate ← đổi vitals.respiratory_rate thành số; lỗi/rỗng → 0</t>
+          <t>if (is_numeric($vitals["respiratory_rate"] ?? null)) {
+    $vitalSigns["respiratoryRate"] = 0 + $vitals["respiratory_rate"];
+} else {
+    $vitalSigns["respiratoryRate"] = 0;
+}</t>
         </is>
       </c>
       <c r="K39" s="26" t="inlineStr">
@@ -5805,7 +5842,11 @@
       </c>
       <c r="J40" s="24" t="inlineStr">
         <is>
-          <t>weight ← đổi vitals.weight_kg thành số; lỗi/rỗng → 0</t>
+          <t>if (is_numeric($vitals["weight_kg"] ?? null)) {
+    $vitalSigns["weight"] = 0 + $vitals["weight_kg"];
+} else {
+    $vitalSigns["weight"] = 0;
+}</t>
         </is>
       </c>
       <c r="K40" s="26" t="inlineStr">
@@ -5887,7 +5928,11 @@
       </c>
       <c r="J41" s="24" t="inlineStr">
         <is>
-          <t>height ← đổi vitals.height_cm thành số; lỗi/rỗng → 0</t>
+          <t>if (is_numeric($vitals["height_cm"] ?? null)) {
+    $vitalSigns["height"] = 0 + $vitals["height_cm"];
+} else {
+    $vitalSigns["height"] = 0;
+}</t>
         </is>
       </c>
       <c r="K41" s="26" t="inlineStr">
@@ -5969,7 +6014,11 @@
       </c>
       <c r="J42" s="24" t="inlineStr">
         <is>
-          <t>temperature ← đổi vitals.temperature thành số; lỗi/rỗng → 0</t>
+          <t>if (is_numeric($vitals["temperature"] ?? null)) {
+    $vitalSigns["temperature"] = 0 + $vitals["temperature"];
+} else {
+    $vitalSigns["temperature"] = 0;
+}</t>
         </is>
       </c>
       <c r="K42" s="26" t="inlineStr">
@@ -6046,7 +6095,11 @@
       </c>
       <c r="J43" s="24" t="inlineStr">
         <is>
-          <t>bmi ← đổi vitals.bmi thành số; lỗi/rỗng → 0</t>
+          <t>if (is_numeric($vitals["bmi"] ?? null)) {
+    $vitalSigns["bmi"] = 0 + $vitals["bmi"];
+} else {
+    $vitalSigns["bmi"] = 0;
+}</t>
         </is>
       </c>
       <c r="K43" s="26" t="inlineStr">
@@ -6249,9 +6302,7 @@
       </c>
       <c r="J46" s="24" t="inlineStr">
         <is>
-          <t>nutrition ← examination.nutrition_assessment
-NẾU không có → thử key 'nutrition assessment'; cuối cùng → ''
-Lưu ý: code không kiểm tra specialty Nhi.</t>
+          <t>$pediatrics["nutrition"] = $examination["nutrition_assessment"] ?? $examination["nutrition assessment"] ?? "";</t>
         </is>
       </c>
       <c r="K46" s="26" t="inlineStr">
@@ -6333,9 +6384,7 @@
       </c>
       <c r="J47" s="24" t="inlineStr">
         <is>
-          <t>vaccination ← examination.vaccination_assessment
-NẾU không có → thử key 'vaccination assessment'; cuối cùng → ''
-Lưu ý: code không kiểm tra specialty Nhi.</t>
+          <t>$pediatrics["vaccination"] = $examination["vaccination_assessment"] ?? $examination["vaccination assessment"] ?? "";</t>
         </is>
       </c>
       <c r="K47" s="26" t="inlineStr">
@@ -6417,9 +6466,7 @@
       </c>
       <c r="J48" s="24" t="inlineStr">
         <is>
-          <t>motorDevelopment ← examination.motor_development
-NẾU không có → thử key 'motor development'; cuối cùng → ''
-Lưu ý: code không kiểm tra specialty Nhi.</t>
+          <t>$pediatrics["motorDevelopment"] = $examination["motor_development"] ?? $examination["motor development"] ?? "";</t>
         </is>
       </c>
       <c r="K48" s="26" t="inlineStr">
@@ -6501,9 +6548,7 @@
       </c>
       <c r="J49" s="24" t="inlineStr">
         <is>
-          <t>mentalDevelopment ← examination.mental_development
-NẾU không có → thử key 'mental development'; cuối cùng → ''
-Lưu ý: code không kiểm tra specialty Nhi.</t>
+          <t>$pediatrics["mentalDevelopment"] = $examination["mental_development"] ?? $examination["mental development"] ?? "";</t>
         </is>
       </c>
       <c r="K49" s="26" t="inlineStr">
@@ -6765,9 +6810,10 @@
       </c>
       <c r="J53" s="24" t="inlineStr">
         <is>
-          <t>GỘP diagnosis_primary + diagnosis_comorbidities
-→ code ← diagnosisItem.code
-SAU ĐÓ bỏ chẩn đoán trùng theo code hoặc tên gần giống</t>
+          <t>foreach ($diagnosisGroups as $diagnosisItem) {
+    $mappedDiagnosis["code"] = $diagnosisItem["code"] ?? "";
+}
+$diagnoses = deduplicateDiagnoses($diagnoses);</t>
         </is>
       </c>
       <c r="K53" s="26" t="inlineStr">
@@ -6880,8 +6926,11 @@
       </c>
       <c r="J54" s="24" t="inlineStr">
         <is>
-          <t>description ← diagnosisItem.description
-NẾU rỗng → null; khi gộp trùng thì giữ description có dữ liệu</t>
+          <t>if (!empty($diagnosisItem["description"])) {
+    $mappedDiagnosis["description"] = $diagnosisItem["description"];
+} else {
+    $mappedDiagnosis["description"] = null;
+}</t>
         </is>
       </c>
       <c r="K54" s="26" t="inlineStr">
@@ -6976,8 +7025,10 @@
       </c>
       <c r="J55" s="24" t="inlineStr">
         <is>
-          <t>name ← diagnosisItem.name
-SAU ĐÓ bỏ chẩn đoán trùng theo code hoặc tên gần giống</t>
+          <t>foreach ($diagnosisGroups as $diagnosisItem) {
+    $mappedDiagnosis["name"] = $diagnosisItem["name"] ?? "";
+}
+$diagnoses = deduplicateDiagnoses($diagnoses);</t>
         </is>
       </c>
       <c r="K55" s="26" t="inlineStr">
@@ -7070,8 +7121,13 @@
       </c>
       <c r="J56" s="24" t="inlineStr">
         <is>
-          <t>TÁCH plan.treatment_plan theo dấu ';'
-Bỏ phần rỗng/vô nghĩa, viết hoa đầu câu → treatment[]</t>
+          <t>$treatment = [];
+foreach (explode(";", $plan["treatment_plan"] ?? "") as $part) {
+    $part = trim($part);
+    if ($part !== "" &amp;&amp; !isGarbage($part)) {
+        $treatment[] = ucfirst($part);
+    }
+}</t>
         </is>
       </c>
       <c r="K56" s="26" t="inlineStr">
@@ -7152,9 +7208,12 @@
       </c>
       <c r="J57" s="44" t="inlineStr">
         <is>
-          <t>NẾU plan.doctor_advice không rỗng/vô nghĩa
-→ advice ← [doctor_advice đã viết hoa đầu câu]
-NGƯỢC LẠI → []</t>
+          <t>$adviceText = trim($plan["doctor_advice"] ?? "");
+if ($adviceText !== "" &amp;&amp; !isGarbage($adviceText)) {
+    $advice = [ucfirst($adviceText)];
+} else {
+    $advice = [];
+}</t>
         </is>
       </c>
       <c r="K57" s="45" t="inlineStr">
@@ -7232,9 +7291,12 @@
       </c>
       <c r="J58" s="24" t="inlineStr">
         <is>
-          <t>TÌM lượt cũ gần nhất có cùng specialty
-SO SÁNH blood_pressure, weight_kg và paraclinical_result
-CHỈ tạo trend khi cả hai lượt có dữ liệu và giá trị thay đổi</t>
+          <t>$previousVisit = findPreviousSameSpecialty($currentVisit, $visits);
+if ($previousVisit === null) {
+    $trends = [];
+} else {
+    $trends = compareVitalsAndParaclinical($previousVisit, $currentVisit);
+}</t>
         </is>
       </c>
       <c r="K58" s="26" t="inlineStr">
@@ -7336,7 +7398,11 @@
       </c>
       <c r="J59" s="24" t="inlineStr">
         <is>
-          <t>trend.name ← 'Huyết áp'/'Cân nặng' hoặc tên xét nghiệm trùng nhau.</t>
+          <t>if ($source === "vital") {
+    $trend["name"] = $vitalLabel;
+} else {
+    $trend["name"] = $currentResult["name"];
+}</t>
         </is>
       </c>
       <c r="K59" s="26" t="inlineStr">
@@ -7418,7 +7484,7 @@
       </c>
       <c r="J60" s="24" t="inlineStr">
         <is>
-          <t>trend.from ← giá trị ở lượt cũ gần nhất cùng specialty.</t>
+          <t>$trend["from"] = $previousValue;</t>
         </is>
       </c>
       <c r="K60" s="26" t="inlineStr">
@@ -7498,7 +7564,7 @@
       </c>
       <c r="J61" s="24" t="inlineStr">
         <is>
-          <t>trend.fromDate ← visit_date của lượt cũ gần nhất cùng specialty.</t>
+          <t>$trend["fromDate"] = $previousVisit["visit_date"] ?? "";</t>
         </is>
       </c>
       <c r="K61" s="26" t="inlineStr">
@@ -7579,7 +7645,7 @@
       </c>
       <c r="J62" s="24" t="inlineStr">
         <is>
-          <t>trend.to ← giá trị ở lượt hiện tại.</t>
+          <t>$trend["to"] = $currentValue;</t>
         </is>
       </c>
       <c r="K62" s="26" t="inlineStr">
@@ -7658,7 +7724,7 @@
       </c>
       <c r="J63" s="24" t="inlineStr">
         <is>
-          <t>trend.toDate ← visit_date của lượt hiện tại.</t>
+          <t>$trend["toDate"] = $currentVisit["visit_date"] ?? "";</t>
         </is>
       </c>
       <c r="K63" s="26" t="inlineStr">
@@ -7812,9 +7878,13 @@
       </c>
       <c r="J65" s="24" t="inlineStr">
         <is>
-          <t>CHO MỖI selectedVisit có followup_date
-→ tạo {specialty, date, valid, note}
-Bỏ trùng theo specialty + date</t>
+          <t>$followUp = [];
+foreach ($selectedVisits as $visit) {
+    $followupDate = $visit["plan"]["followup_date"] ?? "";
+    if ($followupDate !== "" &amp;&amp; !existsSameSpecialtyAndDate($followUp, $visit)) {
+        $followUp[] = buildFollowUpItem($visit, $today);
+    }
+}</t>
         </is>
       </c>
       <c r="K65" s="26" t="inlineStr">
@@ -7894,7 +7964,7 @@
       </c>
       <c r="J66" s="24" t="inlineStr">
         <is>
-          <t>followUp.specialty ← selectedVisit.specialty</t>
+          <t>$followUpItem["specialty"] = $visit["specialty"] ?? "";</t>
         </is>
       </c>
       <c r="K66" s="26" t="inlineStr">
@@ -7974,7 +8044,11 @@
       </c>
       <c r="J67" s="24" t="inlineStr">
         <is>
-          <t>followUp.date ← chuẩn hóa plan.followup_date thành YYYY-MM-DD; sai ngày → ''</t>
+          <t>if (isValidDate($followupDate)) {
+    $followUpItem["date"] = formatDate($followupDate, "Y-m-d");
+} else {
+    $followUpItem["date"] = "";
+}</t>
         </is>
       </c>
       <c r="K67" s="26" t="inlineStr">
@@ -8062,8 +8136,11 @@
       </c>
       <c r="J68" s="24" t="inlineStr">
         <is>
-          <t>valid ← TRUE khi followup_date và visit_date đều hợp lệ
-VÀ followup_date &gt; visit_date; còn lại FALSE</t>
+          <t>if (isValidDate($followupDate) &amp;&amp; isValidDate($visitDate) &amp;&amp; $followupDate &gt; $visitDate) {
+    $followUpItem["valid"] = true;
+} else {
+    $followUpItem["valid"] = false;
+}</t>
         </is>
       </c>
       <c r="K68" s="26" t="inlineStr">
@@ -8146,10 +8223,15 @@
       </c>
       <c r="J69" s="24" t="inlineStr">
         <is>
-          <t>note ← 'Không đủ dữ liệu...' nếu ngày không parse được
-note ← 'Quá hạn' nếu ngày hẹn hợp lệ nhưng trước hôm nay
-note ← 'Ngày hẹn không hợp lệ...' nếu ngày hẹn ≤ ngày khám
-còn lại note ← ''</t>
+          <t>if (!isValidDate($followupDate) || !isValidDate($visitDate)) {
+    $followUpItem["note"] = "Không đủ dữ liệu xác định tính hợp lệ";
+} else if ($followupDate &lt;= $visitDate) {
+    $followUpItem["note"] = "Ngày hẹn không hợp lệ";
+} else if ($followupDate &lt; $today) {
+    $followUpItem["note"] = "Quá hạn";
+} else {
+    $followUpItem["note"] = "";
+}</t>
         </is>
       </c>
       <c r="K69" s="26" t="inlineStr">
@@ -8282,7 +8364,7 @@
       </c>
       <c r="J71" s="24" t="inlineStr">
         <is>
-          <t>timeline.visitDate ← visit.visit_date</t>
+          <t>$timelineItem["visitDate"] = $visit["visit_date"] ?? "";</t>
         </is>
       </c>
       <c r="K71" s="26" t="inlineStr">
@@ -8358,7 +8440,7 @@
       </c>
       <c r="J72" s="24" t="inlineStr">
         <is>
-          <t>timeline.specialty ← visit.specialty</t>
+          <t>$timelineItem["specialty"] = $visit["specialty"] ?? "";</t>
         </is>
       </c>
       <c r="K72" s="26" t="inlineStr">
@@ -8434,7 +8516,7 @@
       </c>
       <c r="J73" s="24" t="inlineStr">
         <is>
-          <t>timeline.visitCode ← visit.visit_code</t>
+          <t>$timelineItem["visitCode"] = $visit["visit_code"] ?? "";</t>
         </is>
       </c>
       <c r="K73" s="26" t="inlineStr">
@@ -8761,8 +8843,10 @@
       </c>
       <c r="J78" s="24" t="inlineStr">
         <is>
-          <t>GỘP diagnosis_primary + diagnosis_comorbidities của visit
-→ diagnosis.code ← diagnosisItem.code; sau đó bỏ trùng</t>
+          <t>foreach ($visitDiagnosisItems as $diagnosisItem) {
+    $timelineDiagnosis["code"] = $diagnosisItem["code"] ?? "";
+}
+$timelineDiagnoses = deduplicateDiagnoses($timelineDiagnoses);</t>
         </is>
       </c>
       <c r="K78" s="26" t="inlineStr">
@@ -8843,8 +8927,11 @@
       </c>
       <c r="J79" s="24" t="inlineStr">
         <is>
-          <t>diagnosis.description ← diagnosisItem.description
-NẾU rỗng → null; không lấy diagnosis_text trong code hiện tại</t>
+          <t>if (!empty($diagnosisItem["description"])) {
+    $timelineDiagnosis["description"] = $diagnosisItem["description"];
+} else {
+    $timelineDiagnosis["description"] = null;
+}</t>
         </is>
       </c>
       <c r="K79" s="26" t="inlineStr">
@@ -8923,7 +9010,10 @@
       </c>
       <c r="J80" s="24" t="inlineStr">
         <is>
-          <t>diagnosis.name ← diagnosisItem.name; sau đó bỏ trùng theo code/tên.</t>
+          <t>foreach ($visitDiagnosisItems as $diagnosisItem) {
+    $timelineDiagnosis["name"] = $diagnosisItem["name"] ?? "";
+}
+$timelineDiagnoses = deduplicateDiagnoses($timelineDiagnoses);</t>
         </is>
       </c>
       <c r="K80" s="26" t="inlineStr">
@@ -9003,8 +9093,12 @@
       </c>
       <c r="J81" s="24" t="inlineStr">
         <is>
-          <t>LẤY toàn bộ plan.treatment_plan làm một phần tử treatment[]
-Không tách theo dấu ';'; bỏ nếu rỗng/vô nghĩa</t>
+          <t>$treatmentPlan = trim($visit["plan"]["treatment_plan"] ?? "");
+if ($treatmentPlan !== "" &amp;&amp; !isGarbage($treatmentPlan)) {
+    $timelineTreatment = [ucfirst($treatmentPlan)];
+} else {
+    $timelineTreatment = [];
+}</t>
         </is>
       </c>
       <c r="K81" s="26" t="inlineStr">
@@ -9092,9 +9186,18 @@
       </c>
       <c r="J82" s="44" t="inlineStr">
         <is>
-          <t>CHO MỖI item trong prescriptions[] của chính visit
-Bỏ item không có name
-Tạo chuỗi: name + tần suất rút gọn + (duration)</t>
+          <t>$prescriptionSummary = [];
+foreach ($visit["prescriptions"] ?? [] as $prescription) {
+    foreach ($prescription["items"] ?? [] as $item) {
+        $name = trim($item["name"] ?? "");
+        if ($name === "") { continue; }
+        $text = $name;
+        $frequency = abbreviateFrequency($item["dosage_instruction"] ?? "");
+        if ($frequency !== "") { $text .= " " . $frequency; }
+        if (!empty($item["duration"])) { $text .= " (" . $item["duration"] . ")"; }
+        $prescriptionSummary[] = $text;
+    }
+}</t>
         </is>
       </c>
       <c r="K82" s="45" t="inlineStr">
@@ -9255,8 +9358,7 @@
       </c>
       <c r="J84" s="24" t="inlineStr">
         <is>
-          <t>nutrition ← examination.nutrition_assessment hoặc key có dấu cách
-Lưu ý: code không kiểm tra specialty Nhi.</t>
+          <t>$timelinePediatrics["nutrition"] = $examination["nutrition_assessment"] ?? $examination["nutrition assessment"] ?? "";</t>
         </is>
       </c>
       <c r="K84" s="26" t="inlineStr">
@@ -9339,8 +9441,7 @@
       </c>
       <c r="J85" s="24" t="inlineStr">
         <is>
-          <t>vaccination ← examination.vaccination_assessment hoặc key có dấu cách
-Lưu ý: code không kiểm tra specialty Nhi.</t>
+          <t>$timelinePediatrics["vaccination"] = $examination["vaccination_assessment"] ?? $examination["vaccination assessment"] ?? "";</t>
         </is>
       </c>
       <c r="K85" s="26" t="inlineStr">
@@ -9423,8 +9524,7 @@
       </c>
       <c r="J86" s="24" t="inlineStr">
         <is>
-          <t>motorDevelopment ← examination.motor_development hoặc key có dấu cách
-Lưu ý: code không kiểm tra specialty Nhi.</t>
+          <t>$timelinePediatrics["motorDevelopment"] = $examination["motor_development"] ?? $examination["motor development"] ?? "";</t>
         </is>
       </c>
       <c r="K86" s="26" t="inlineStr">
@@ -9507,8 +9607,7 @@
       </c>
       <c r="J87" s="24" t="inlineStr">
         <is>
-          <t>mentalDevelopment ← examination.mental_development hoặc key có dấu cách
-Lưu ý: code không kiểm tra specialty Nhi.</t>
+          <t>$timelinePediatrics["mentalDevelopment"] = $examination["mental_development"] ?? $examination["mental development"] ?? "";</t>
         </is>
       </c>
       <c r="K87" s="26" t="inlineStr">
@@ -9718,7 +9817,7 @@
       </c>
       <c r="J90" s="24" t="inlineStr">
         <is>
-          <t>errors ← {}  (code hiện luôn trả object rỗng)</t>
+          <t>$output["errors"] = new stdClass();</t>
         </is>
       </c>
       <c r="K90" s="26" t="inlineStr">
@@ -9778,7 +9877,8 @@
       </c>
       <c r="J91" s="24" t="inlineStr">
         <is>
-          <t>KHÔNG DÙNG patient.pseudo_id trong mapper.py → không có output trực tiếp.</t>
+          <t>$pseudoId = $patient["pseudo_id"] ?? null;
+// Không gán $pseudoId vào output.</t>
         </is>
       </c>
       <c r="K91" s="26" t="inlineStr">
@@ -9842,7 +9942,8 @@
       </c>
       <c r="J92" s="24" t="inlineStr">
         <is>
-          <t>KHÔNG DÙNG visits[].clinic trong mapper.py → không có output trực tiếp.</t>
+          <t>$clinic = $visit["clinic"] ?? null;
+// Không gán $clinic vào output.</t>
         </is>
       </c>
       <c r="K92" s="26" t="inlineStr">
@@ -9909,8 +10010,8 @@
       </c>
       <c r="J93" s="24" t="inlineStr">
         <is>
-          <t>KHÔNG DÙNG current_medications[].last_dose_date trong mapper.py
-→ không có output trực tiếp.</t>
+          <t>$lastDoseDate = $medication["last_dose_date"] ?? null;
+// Không gán $lastDoseDate vào output.</t>
         </is>
       </c>
       <c r="K93" s="26" t="inlineStr">
@@ -9969,7 +10070,8 @@
       </c>
       <c r="J94" s="24" t="inlineStr">
         <is>
-          <t>KHÔNG DÙNG prescriptions[].prescriber trong mapper.py → không có output trực tiếp.</t>
+          <t>$prescriber = $prescription["prescriber"] ?? null;
+// Không gán $prescriber vào output.</t>
         </is>
       </c>
       <c r="K94" s="26" t="inlineStr">
@@ -10036,8 +10138,9 @@
       </c>
       <c r="J95" s="24" t="inlineStr">
         <is>
-          <t>diagnosis_on_prescription được gom vào dữ liệu đầu vào AI của oneLiner
-Code hiện không dùng nó cho Tiền sử nền hoặc Timeline.</t>
+          <t>foreach ($visit["prescriptions"] ?? [] as $prescription) {
+    $oneLinerInputs[] = $prescription["diagnosis_on_prescription"] ?? null;
+}</t>
         </is>
       </c>
       <c r="K95" s="26" t="inlineStr">
@@ -10116,9 +10219,12 @@
       </c>
       <c r="J96" s="24" t="inlineStr">
         <is>
-          <t>stop_date dùng để xác định thuốc còn hạn:
-còn hạn khi parse được ngày VÀ stop_date ≥ hôm nay
-Kết quả ảnh hưởng byPrescription, selectedVisits và followUpItems.</t>
+          <t>$stopDate = $item["stop_date"] ?? null;
+if (isValidDate($stopDate) &amp;&amp; $stopDate &gt;= $today) {
+    $isActive = true;
+} else {
+    $isActive = false;
+}</t>
         </is>
       </c>
       <c r="K96" s="26" t="inlineStr">
@@ -10186,8 +10292,8 @@
       </c>
       <c r="J97" s="24" t="inlineStr">
         <is>
-          <t>KHÔNG DÙNG diagnosis_from_referring_facility trong mapper.py
-→ không có output trực tiếp.</t>
+          <t>$referringDiagnosis = $visit["diagnosis"]["diagnosis_from_referring_facility"] ?? null;
+// Không gán $referringDiagnosis vào output.</t>
         </is>
       </c>
       <c r="K97" s="26" t="inlineStr">
@@ -10287,9 +10393,13 @@
       </c>
       <c r="J98" s="24" t="inlineStr">
         <is>
-          <t>CHO MỖI diagnosis_primary[]
-→ description ← item.description; nếu rỗng → null
-Dùng chung cho latestBySpecialty và timeline.</t>
+          <t>foreach ($diagnosis["diagnosis_primary"] ?? [] as $item) {
+    if (!empty($item["description"])) {
+        $mappedDiagnosis["description"] = $item["description"];
+    } else {
+        $mappedDiagnosis["description"] = null;
+    }
+}</t>
         </is>
       </c>
       <c r="K98" s="26" t="inlineStr">
@@ -10382,9 +10492,13 @@
       </c>
       <c r="J99" s="24" t="inlineStr">
         <is>
-          <t>CHO MỖI diagnosis_comorbidities[]
-→ description ← item.description; nếu rỗng → null
-Dùng chung cho latestBySpecialty và timeline.</t>
+          <t>foreach ($diagnosis["diagnosis_comorbidities"] ?? [] as $item) {
+    if (!empty($item["description"])) {
+        $mappedDiagnosis["description"] = $item["description"];
+    } else {
+        $mappedDiagnosis["description"] = null;
+    }
+}</t>
         </is>
       </c>
       <c r="K99" s="26" t="inlineStr">
